--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3519</v>
+        <v>13.0665</v>
       </c>
       <c r="E2" t="n">
-        <v>18.7389</v>
+        <v>21.6292</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.3867</v>
+        <v>-8.562100000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>9.567600000000001</v>
+        <v>11.2929</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.334899999999999</v>
+        <v>-4.2443</v>
       </c>
       <c r="I2" t="n">
-        <v>14.9028</v>
+        <v>15.5371</v>
       </c>
       <c r="J2" t="n">
-        <v>21.6771</v>
+        <v>26.7966</v>
       </c>
       <c r="K2" t="n">
-        <v>5.891100000000001</v>
+        <v>8.1426</v>
       </c>
       <c r="L2" t="n">
-        <v>15.786</v>
+        <v>18.6537</v>
       </c>
       <c r="M2" t="n">
-        <v>-12.1095</v>
+        <v>-15.5034</v>
       </c>
       <c r="N2" t="n">
-        <v>-11.226</v>
+        <v>-12.3872</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8835</v>
+        <v>-3.1166</v>
       </c>
       <c r="P2" t="n">
-        <v>-13.1529</v>
+        <v>-15.6223</v>
       </c>
       <c r="Q2" t="n">
-        <v>-21.4602</v>
+        <v>-26.814</v>
       </c>
       <c r="R2" t="n">
-        <v>8.307</v>
+        <v>11.192</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.9251</v>
+        <v>-5.5359</v>
       </c>
       <c r="T2" t="n">
-        <v>-4.095</v>
+        <v>-4.1063</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8297999999999999</v>
+        <v>-1.4296</v>
       </c>
       <c r="V2" t="n">
-        <v>20.8623</v>
+        <v>22.9318</v>
       </c>
       <c r="W2" t="n">
-        <v>22.6167</v>
+        <v>25.7532</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7544</v>
+        <v>-2.8214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>2.892000000000001</v>
+        <v>3.2811</v>
       </c>
       <c r="E3" t="n">
-        <v>18.2253</v>
+        <v>7.7905</v>
       </c>
       <c r="F3" t="n">
-        <v>-15.333</v>
+        <v>-4.5097</v>
       </c>
       <c r="G3" t="n">
-        <v>10.3269</v>
+        <v>8.304600000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.9391</v>
+        <v>-13.3972</v>
       </c>
       <c r="I3" t="n">
-        <v>13.266</v>
+        <v>21.7022</v>
       </c>
       <c r="J3" t="n">
-        <v>28.4919</v>
+        <v>20.2709</v>
       </c>
       <c r="K3" t="n">
-        <v>8.2989</v>
+        <v>2.277399999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>20.193</v>
+        <v>17.9939</v>
       </c>
       <c r="M3" t="n">
-        <v>-18.1644</v>
+        <v>-11.9666</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.238</v>
+        <v>-15.6745</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.927</v>
+        <v>3.7083</v>
       </c>
       <c r="P3" t="n">
-        <v>-9.6915</v>
+        <v>9.7928</v>
       </c>
       <c r="Q3" t="n">
-        <v>-17.3064</v>
+        <v>-7.2282</v>
       </c>
       <c r="R3" t="n">
-        <v>7.6149</v>
+        <v>17.0213</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.0285</v>
+        <v>-4.1584</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.969</v>
+        <v>-5.2523</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9401999999999999</v>
+        <v>1.0936</v>
       </c>
       <c r="V3" t="n">
-        <v>5.2851</v>
+        <v>-10.6583</v>
       </c>
       <c r="W3" t="n">
-        <v>11.0088</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.7237</v>
+        <v>-10.6583</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8668</v>
+        <v>2.8005</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4696</v>
+        <v>3.2518</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6028</v>
+        <v>-0.4514</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2738</v>
+        <v>0.821</v>
       </c>
       <c r="H4" t="n">
-        <v>-14.925</v>
+        <v>0.6113</v>
       </c>
       <c r="I4" t="n">
-        <v>19.1988</v>
+        <v>0.2098</v>
       </c>
       <c r="J4" t="n">
-        <v>13.0518</v>
+        <v>2.0159</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.7221</v>
+        <v>0.5852999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>19.7736</v>
+        <v>1.4307</v>
       </c>
       <c r="M4" t="n">
-        <v>-8.7783</v>
+        <v>-1.195</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.203200000000001</v>
+        <v>0.02599999999999997</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5747999999999995</v>
+        <v>-1.2209</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6924</v>
+        <v>-0.2332</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.3073</v>
+        <v>-1.6322</v>
       </c>
       <c r="R4" t="n">
-        <v>8.9994</v>
+        <v>1.399</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.1535</v>
+        <v>-0.3336</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.9448</v>
+        <v>0.1997</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2087</v>
+        <v>-0.5333</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0541</v>
+        <v>2.5461</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6696</v>
+        <v>2.6684</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6155</v>
+        <v>-0.1222000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1952</v>
+        <v>-0.9668000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8516999999999998</v>
+        <v>-0.4973999999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3435000000000001</v>
+        <v>-0.4695000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0415</v>
+        <v>-0.8082999999999997</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0002</v>
+        <v>-2.9633</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0414</v>
+        <v>2.1549</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3289</v>
+        <v>4.4877</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6198</v>
+        <v>3.6308</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7091</v>
+        <v>0.8568999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.2874</v>
+        <v>-5.296</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.6197</v>
+        <v>-6.5937</v>
       </c>
       <c r="O5" t="n">
-        <v>1.332</v>
+        <v>1.2978</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6924</v>
+        <v>1.8654</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1538</v>
+        <v>-4.197</v>
       </c>
       <c r="R5" t="n">
-        <v>4.8462</v>
+        <v>6.0624</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0998</v>
+        <v>-1.612</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.5544</v>
+        <v>-3.9899</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4543</v>
+        <v>2.3779</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4386</v>
+        <v>-0.4119</v>
       </c>
       <c r="W5" t="n">
-        <v>3.231</v>
+        <v>3.2019</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.6696</v>
+        <v>-3.6138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>D. BORDON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6135000000000004</v>
+        <v>-1.4343</v>
       </c>
       <c r="E6" t="n">
-        <v>3.168</v>
+        <v>-1.8771</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5545</v>
+        <v>0.4428</v>
       </c>
       <c r="G6" t="n">
-        <v>5.004899999999999</v>
+        <v>-4.991400000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-15.4167</v>
+        <v>-3.4764</v>
       </c>
       <c r="I6" t="n">
-        <v>20.4216</v>
+        <v>-1.515</v>
       </c>
       <c r="J6" t="n">
-        <v>12.5229</v>
+        <v>-5.0007</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.616400000000001</v>
+        <v>-2.4753</v>
       </c>
       <c r="L6" t="n">
-        <v>14.1399</v>
+        <v>-2.5254</v>
       </c>
       <c r="M6" t="n">
-        <v>-7.518</v>
+        <v>0.009299999999999975</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.8</v>
+        <v>-1.0011</v>
       </c>
       <c r="O6" t="n">
-        <v>6.282</v>
+        <v>1.0104</v>
       </c>
       <c r="P6" t="n">
-        <v>8.9994</v>
+        <v>0.6996</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1538</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>13.1532</v>
+        <v>0.6996</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.2595</v>
+        <v>0.0675</v>
       </c>
       <c r="T6" t="n">
-        <v>-5.2014</v>
+        <v>-0.07830000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9419</v>
+        <v>0.1458</v>
       </c>
       <c r="V6" t="n">
-        <v>-10.1316</v>
+        <v>2.79</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.2019</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.1316</v>
+        <v>-0.4119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. BORDON</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4355</v>
+        <v>-3.3143</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8237</v>
+        <v>14.7279</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3885</v>
+        <v>-18.0422</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.0031</v>
+        <v>5.086599999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.4887</v>
+        <v>-4.852</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5144</v>
+        <v>9.938600000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.9971</v>
+        <v>26.3752</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.4732</v>
+        <v>7.036</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.5239</v>
+        <v>19.3393</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.005699999999999955</v>
+        <v>-21.2886</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0155</v>
+        <v>-11.8879</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0098</v>
+        <v>-9.400700000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6924</v>
+        <v>-10.4924</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-19.353</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6924</v>
+        <v>8.860300000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08309999999999999</v>
+        <v>-3.4434</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0576</v>
+        <v>-4.2035</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1407</v>
+        <v>0.7598</v>
       </c>
       <c r="V7" t="n">
-        <v>2.7924</v>
+        <v>5.5351</v>
       </c>
       <c r="W7" t="n">
-        <v>3.231</v>
+        <v>11.9087</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4386</v>
+        <v>-6.3739</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.734200000000001</v>
+        <v>-5.188599999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>15.2367</v>
+        <v>0.5875999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-20.9709</v>
+        <v>-5.7763</v>
       </c>
       <c r="G8" t="n">
-        <v>9.9861</v>
+        <v>0.4431000000000008</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2765999999999997</v>
+        <v>-18.2269</v>
       </c>
       <c r="I8" t="n">
-        <v>10.2627</v>
+        <v>18.67</v>
       </c>
       <c r="J8" t="n">
-        <v>25.7631</v>
+        <v>12.1075</v>
       </c>
       <c r="K8" t="n">
-        <v>11.5044</v>
+        <v>-8.6991</v>
       </c>
       <c r="L8" t="n">
-        <v>14.2587</v>
+        <v>20.8066</v>
       </c>
       <c r="M8" t="n">
-        <v>-15.777</v>
+        <v>-11.6645</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.781</v>
+        <v>-9.527799999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.9963</v>
+        <v>-2.1367</v>
       </c>
       <c r="P8" t="n">
-        <v>6.2301</v>
+        <v>-1.8655</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7.6149</v>
+        <v>-13.524</v>
       </c>
       <c r="R8" t="n">
-        <v>13.8453</v>
+        <v>11.6585</v>
       </c>
       <c r="S8" t="n">
-        <v>-7.272</v>
+        <v>-6.206399999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-6.1425</v>
+        <v>-3.745</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1295</v>
+        <v>-2.4617</v>
       </c>
       <c r="V8" t="n">
-        <v>-14.6784</v>
+        <v>2.4399</v>
       </c>
       <c r="W8" t="n">
-        <v>3.231</v>
+        <v>5.748399999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-17.9094</v>
+        <v>-3.3088</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>E. FRIDRIKSSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.754499999999999</v>
+        <v>-12.3056</v>
       </c>
       <c r="E9" t="n">
-        <v>7.720800000000001</v>
+        <v>-12.0888</v>
       </c>
       <c r="F9" t="n">
-        <v>-14.4753</v>
+        <v>-0.2168</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.583899999999999</v>
+        <v>-1.4864</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.5954</v>
+        <v>-1.9578</v>
       </c>
       <c r="I9" t="n">
-        <v>5.0115</v>
+        <v>0.4714</v>
       </c>
       <c r="J9" t="n">
-        <v>6.182399999999999</v>
+        <v>-0.5245</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9281</v>
+        <v>2.6477</v>
       </c>
       <c r="L9" t="n">
-        <v>8.1099</v>
+        <v>-3.172200000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-8.766299999999999</v>
+        <v>-0.9619000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.6673</v>
+        <v>-4.6055</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.0987</v>
+        <v>3.6436</v>
       </c>
       <c r="P9" t="n">
-        <v>8.999700000000001</v>
+        <v>-5.1296</v>
       </c>
       <c r="Q9" t="n">
+        <v>-9.3268</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.1972</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-3.2647</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-2.2375</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.0272</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-2.4246</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>8.999700000000001</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-2.3001</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-2.5698</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.2694</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-10.8699</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4.1082</v>
-      </c>
       <c r="X9" t="n">
-        <v>-14.9781</v>
+        <v>-2.4246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. FRIDRIKSSON</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.6655</v>
+        <v>-12.9289</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.619299999999999</v>
+        <v>3.2529</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.04619999999999991</v>
+        <v>-16.1818</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03990000000000027</v>
+        <v>-8.8919</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.02070000000000038</v>
+        <v>-13.7125</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06030000000000002</v>
+        <v>4.8205</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6032999999999995</v>
+        <v>1.6825</v>
       </c>
       <c r="K10" t="n">
-        <v>4.0767</v>
+        <v>-6.3627</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.4734</v>
+        <v>8.0449</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5636999999999999</v>
+        <v>-10.5744</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.0974</v>
+        <v>-7.3498</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5337</v>
+        <v>-3.2246</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.4611</v>
+        <v>9.326499999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.9225</v>
+        <v>-2.0985</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4614</v>
+        <v>11.425</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.751</v>
+        <v>-3.2851</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.2998</v>
+        <v>-2.4914</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4511999999999999</v>
+        <v>-0.7937</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4927</v>
+        <v>-10.0786</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>6.160399999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4927</v>
+        <v>-16.2387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. YEBO</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.8934</v>
+        <v>-13.7394</v>
       </c>
       <c r="E11" t="n">
-        <v>5.011800000000001</v>
+        <v>13.2081</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.9052</v>
+        <v>-26.9472</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7105</v>
+        <v>3.7639</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.24</v>
+        <v>0.8379999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>8.9505</v>
+        <v>2.9253</v>
       </c>
       <c r="J11" t="n">
-        <v>14.3352</v>
+        <v>23.8475</v>
       </c>
       <c r="K11" t="n">
-        <v>7.5306</v>
+        <v>13.6676</v>
       </c>
       <c r="L11" t="n">
-        <v>6.8049</v>
+        <v>10.1798</v>
       </c>
       <c r="M11" t="n">
-        <v>-11.6253</v>
+        <v>-20.0838</v>
       </c>
       <c r="N11" t="n">
-        <v>-13.7706</v>
+        <v>-12.8293</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1456</v>
+        <v>-7.2545</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.461100000000001</v>
+        <v>7.694199999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-11.7684</v>
+        <v>-7.9279</v>
       </c>
       <c r="R11" t="n">
-        <v>8.307</v>
+        <v>15.6221</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.8197</v>
+        <v>-7.9676</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.1562</v>
+        <v>-6.981400000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3365</v>
+        <v>-0.9865000000000002</v>
       </c>
       <c r="V11" t="n">
-        <v>-6.3231</v>
+        <v>-17.2303</v>
       </c>
       <c r="W11" t="n">
-        <v>6.6009</v>
+        <v>4.2695</v>
       </c>
       <c r="X11" t="n">
-        <v>-12.924</v>
+        <v>-21.4998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>K. YEBO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.1142</v>
+        <v>-15.891</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1383</v>
+        <v>2.843800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.9762</v>
+        <v>-18.7346</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.0095</v>
+        <v>-1.0352</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.203799999999999</v>
+        <v>-6.7623</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1949</v>
+        <v>5.727099999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3418</v>
+        <v>13.5001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9644999999999999</v>
+        <v>8.312500000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3767</v>
+        <v>5.1877</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.351000000000001</v>
+        <v>-14.5353</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.168600000000001</v>
+        <v>-15.0745</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1820999999999999</v>
+        <v>0.5394999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3845</v>
+        <v>-3.4974</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.6924</v>
+        <v>-13.2907</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0769</v>
+        <v>9.792999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7968000000000001</v>
+        <v>-2.8659</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.788</v>
+        <v>-3.4194</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9912000000000001</v>
+        <v>0.5534999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-9.693</v>
+        <v>-8.4923</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>6.0542</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.693</v>
+        <v>-14.5465</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. VAN BECK</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,148 +1420,226 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>-37.2402</v>
+        <v>-16.0651</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.3017</v>
+        <v>-0.8338999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-29.9388</v>
+        <v>-15.2315</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.8703</v>
+        <v>-7.2712</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.180400000000001</v>
+        <v>-7.7724</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6896</v>
+        <v>0.5012</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7269</v>
+        <v>2.5089</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0094</v>
+        <v>2.0184</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7175</v>
+        <v>0.4901999999999997</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.5972</v>
+        <v>-9.7798</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.1904</v>
+        <v>-9.7911</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.4074</v>
+        <v>0.0114000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-15.2295</v>
+        <v>1.3989</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.9988</v>
+        <v>-1.8654</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7693</v>
+        <v>3.2643</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.6784</v>
+        <v>-0.5869</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1614</v>
+        <v>-1.4774</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.5173</v>
+        <v>0.8901999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.462</v>
+        <v>-9.606</v>
       </c>
       <c r="W13" t="n">
-        <v>10.1316</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.5936</v>
+        <v>-9.606</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>W. VAN BECK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>La Laguna Tenerife</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-43.5496</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-10.1694</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-33.3799</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-15.7098</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-12.5672</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-3.1432</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.0164</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.4601000000000002</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.4763</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-16.7265</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-12.1066</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-4.6195</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-14.9228</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-18.6536</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.7308</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-6.5435</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-3.221</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-3.3222</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-6.373499999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>10.6885</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-17.0621</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>La Laguna Tenerife</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-65.91810000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>56.5398</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-122.4576</v>
-      </c>
-      <c r="G14" t="n">
-        <v>19.4844</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-73.6215</v>
-      </c>
-      <c r="I14" t="n">
-        <v>93.10650000000001</v>
-      </c>
-      <c r="J14" t="n">
-        <v>129.0282</v>
-      </c>
-      <c r="K14" t="n">
-        <v>31.1556</v>
-      </c>
-      <c r="L14" t="n">
-        <v>97.872</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-109.5438</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-104.7777</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-4.766699999999998</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-17.30520000000001</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-100.3785</v>
-      </c>
-      <c r="R14" t="n">
-        <v>83.0727</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-38.0013</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-39.93990000000001</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.9377</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-30.09539999999999</v>
-      </c>
-      <c r="W14" t="n">
-        <v>67.8288</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-97.92419999999998</v>
+      <c r="C15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-106.2355</v>
+      </c>
+      <c r="E15" t="n">
+        <v>41.8252</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-148.0602</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-10.4821</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-88.483</v>
+      </c>
+      <c r="I15" t="n">
+        <v>77.99989999999998</v>
+      </c>
+      <c r="J15" t="n">
+        <v>129.084</v>
+      </c>
+      <c r="K15" t="n">
+        <v>30.3211</v>
+      </c>
+      <c r="L15" t="n">
+        <v>98.7624</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-139.5665</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-118.803</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-20.7625</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-20.9858</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-125.9113</v>
+      </c>
+      <c r="R15" t="n">
+        <v>104.9255</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-45.73589999999999</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-41.00370000000001</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-4.733400000000001</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-29.0326</v>
+      </c>
+      <c r="W15" t="n">
+        <v>79.6551</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-108.688</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0665</v>
+        <v>3.9383</v>
       </c>
       <c r="E2" t="n">
-        <v>21.6292</v>
+        <v>10.9197</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.562100000000001</v>
+        <v>-6.9813</v>
       </c>
       <c r="G2" t="n">
-        <v>11.2929</v>
+        <v>3.8523</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.2443</v>
+        <v>-1.5804</v>
       </c>
       <c r="I2" t="n">
-        <v>15.5371</v>
+        <v>5.432600000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>26.7966</v>
+        <v>13.0348</v>
       </c>
       <c r="K2" t="n">
-        <v>8.1426</v>
+        <v>2.5704</v>
       </c>
       <c r="L2" t="n">
-        <v>18.6537</v>
+        <v>10.4644</v>
       </c>
       <c r="M2" t="n">
-        <v>-15.5034</v>
+        <v>-9.182699999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-12.3872</v>
+        <v>-4.1507</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.1166</v>
+        <v>-5.0318</v>
       </c>
       <c r="P2" t="n">
-        <v>-15.6223</v>
+        <v>-4.59</v>
       </c>
       <c r="Q2" t="n">
-        <v>-26.814</v>
+        <v>-7.1145</v>
       </c>
       <c r="R2" t="n">
-        <v>11.192</v>
+        <v>2.5245</v>
       </c>
       <c r="S2" t="n">
-        <v>-5.5359</v>
+        <v>-0.7341</v>
       </c>
       <c r="T2" t="n">
-        <v>-4.1063</v>
+        <v>-1.0145</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4296</v>
+        <v>0.2802999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>22.9318</v>
+        <v>5.4101</v>
       </c>
       <c r="W2" t="n">
-        <v>25.7532</v>
+        <v>6.013500000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.8214</v>
+        <v>-0.6034</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2811</v>
+        <v>1.9922</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7905</v>
+        <v>3.1037</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.5097</v>
+        <v>-1.1115</v>
       </c>
       <c r="G3" t="n">
-        <v>8.304600000000001</v>
+        <v>2.6443</v>
       </c>
       <c r="H3" t="n">
-        <v>-13.3972</v>
+        <v>-5.4262</v>
       </c>
       <c r="I3" t="n">
-        <v>21.7022</v>
+        <v>8.070500000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>20.2709</v>
+        <v>8.1957</v>
       </c>
       <c r="K3" t="n">
-        <v>2.277399999999999</v>
+        <v>0.7589000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>17.9939</v>
+        <v>7.4368</v>
       </c>
       <c r="M3" t="n">
-        <v>-11.9666</v>
+        <v>-5.5512</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.6745</v>
+        <v>-6.185</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7083</v>
+        <v>0.6337999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>9.7928</v>
+        <v>3.9015</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7.2282</v>
+        <v>-2.9834</v>
       </c>
       <c r="R3" t="n">
-        <v>17.0213</v>
+        <v>6.885</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.1584</v>
+        <v>-3.17</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.2523</v>
+        <v>-2.1085</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0936</v>
+        <v>-1.0614</v>
       </c>
       <c r="V3" t="n">
-        <v>-10.6583</v>
+        <v>-1.3838</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.6583</v>
+        <v>-1.3838</v>
       </c>
     </row>
     <row r="4">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8005</v>
+        <v>1.328</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2518</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4514</v>
+        <v>0.3305</v>
       </c>
       <c r="G4" t="n">
-        <v>0.821</v>
+        <v>0.5426</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6113</v>
+        <v>0.8761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2098</v>
+        <v>-0.3335</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0159</v>
+        <v>0.6338</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5852999999999999</v>
+        <v>0.5968</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4307</v>
+        <v>0.0371</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.195</v>
+        <v>-0.0912</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02599999999999997</v>
+        <v>0.2793</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2209</v>
+        <v>-0.3705</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2332</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.6322</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.399</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3336</v>
+        <v>-0.5359</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1997</v>
+        <v>-0.1773</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5333</v>
+        <v>-0.3586</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5461</v>
+        <v>1.3213</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6684</v>
+        <v>0.541</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1222000000000001</v>
+        <v>0.7803</v>
       </c>
     </row>
     <row r="5">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9668000000000001</v>
+        <v>1.1196</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4973999999999998</v>
+        <v>1.8428</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4695000000000001</v>
+        <v>-0.7232000000000002</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8082999999999997</v>
+        <v>0.6077000000000004</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.9633</v>
+        <v>-1.2922</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1549</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4877</v>
+        <v>3.216</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6308</v>
+        <v>1.5857</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8568999999999999</v>
+        <v>1.6303</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.296</v>
+        <v>-2.6082</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.5937</v>
+        <v>-2.8779</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2978</v>
+        <v>0.2697000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8654</v>
+        <v>1.377</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.197</v>
+        <v>-0.459</v>
       </c>
       <c r="R5" t="n">
-        <v>6.0624</v>
+        <v>1.836</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.612</v>
+        <v>-0.5633</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.9899</v>
+        <v>-0.9141</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3779</v>
+        <v>0.3508</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4119</v>
+        <v>-0.3018</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2019</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.6138</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="6">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4343</v>
+        <v>-0.286</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8771</v>
+        <v>-0.5596</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4428</v>
+        <v>0.2736</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.991400000000001</v>
+        <v>-1.4558</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.4764</v>
+        <v>-1.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.515</v>
+        <v>-0.3234</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.0007</v>
+        <v>-1.5998</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.4753</v>
+        <v>-0.7914</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.5254</v>
+        <v>-0.8084</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009299999999999975</v>
+        <v>0.1441</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0011</v>
+        <v>-0.341</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0104</v>
+        <v>0.4851</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6996</v>
+        <v>0.2295</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6996</v>
+        <v>0.2295</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0675</v>
+        <v>0.0091</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.07830000000000001</v>
+        <v>-0.0417</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1458</v>
+        <v>0.0509</v>
       </c>
       <c r="V6" t="n">
-        <v>2.79</v>
+        <v>0.9312</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2019</v>
+        <v>1.082</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4119</v>
+        <v>-0.1509</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3143</v>
+        <v>-3.1338</v>
       </c>
       <c r="E7" t="n">
-        <v>14.7279</v>
+        <v>0.5421999999999998</v>
       </c>
       <c r="F7" t="n">
-        <v>-18.0422</v>
+        <v>-3.676</v>
       </c>
       <c r="G7" t="n">
-        <v>5.086599999999998</v>
+        <v>-5.9451</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.852</v>
+        <v>-7.2825</v>
       </c>
       <c r="I7" t="n">
-        <v>9.938600000000001</v>
+        <v>1.3372</v>
       </c>
       <c r="J7" t="n">
-        <v>26.3752</v>
+        <v>-1.3492</v>
       </c>
       <c r="K7" t="n">
-        <v>7.036</v>
+        <v>-4.5252</v>
       </c>
       <c r="L7" t="n">
-        <v>19.3393</v>
+        <v>3.176</v>
       </c>
       <c r="M7" t="n">
-        <v>-21.2886</v>
+        <v>-4.5961</v>
       </c>
       <c r="N7" t="n">
-        <v>-11.8879</v>
+        <v>-2.7573</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.400700000000001</v>
+        <v>-1.8388</v>
       </c>
       <c r="P7" t="n">
-        <v>-10.4924</v>
+        <v>2.9835</v>
       </c>
       <c r="Q7" t="n">
-        <v>-19.353</v>
+        <v>-1.377</v>
       </c>
       <c r="R7" t="n">
-        <v>8.860300000000001</v>
+        <v>4.3605</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.4434</v>
+        <v>-2.0967</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.2035</v>
+        <v>-1.3613</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7598</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5351</v>
+        <v>1.9248</v>
       </c>
       <c r="W7" t="n">
-        <v>11.9087</v>
+        <v>4.6298</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.3739</v>
+        <v>-2.705</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.188599999999999</v>
+        <v>-6.4996</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5875999999999999</v>
+        <v>-3.1145</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.7763</v>
+        <v>-3.385</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4431000000000008</v>
+        <v>-3.834</v>
       </c>
       <c r="H8" t="n">
-        <v>-18.2269</v>
+        <v>-5.1575</v>
       </c>
       <c r="I8" t="n">
-        <v>18.67</v>
+        <v>1.3235</v>
       </c>
       <c r="J8" t="n">
-        <v>12.1075</v>
+        <v>1.973200000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.6991</v>
+        <v>-1.1421</v>
       </c>
       <c r="L8" t="n">
-        <v>20.8066</v>
+        <v>3.1152</v>
       </c>
       <c r="M8" t="n">
-        <v>-11.6645</v>
+        <v>-5.8072</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.527799999999999</v>
+        <v>-4.015499999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1367</v>
+        <v>-1.7915</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8655</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q8" t="n">
-        <v>-13.524</v>
+        <v>-5.7375</v>
       </c>
       <c r="R8" t="n">
-        <v>11.6585</v>
+        <v>4.59</v>
       </c>
       <c r="S8" t="n">
-        <v>-6.206399999999999</v>
+        <v>-2.6001</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.745</v>
+        <v>-1.6651</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.4617</v>
+        <v>-0.9349000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4399</v>
+        <v>1.082</v>
       </c>
       <c r="W8" t="n">
-        <v>5.748399999999999</v>
+        <v>2.3149</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.3088</v>
+        <v>-1.2329</v>
       </c>
     </row>
     <row r="9">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-12.3056</v>
+        <v>-6.5628</v>
       </c>
       <c r="E9" t="n">
-        <v>-12.0888</v>
+        <v>-6.490399999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2168</v>
+        <v>-0.07239999999999991</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4864</v>
+        <v>0.7367000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9578</v>
+        <v>-0.1657999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4714</v>
+        <v>0.9026</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5245</v>
+        <v>1.5159</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6477</v>
+        <v>2.297800000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.172200000000001</v>
+        <v>-0.7817999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9619000000000001</v>
+        <v>-0.7791000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.6055</v>
+        <v>-2.4633</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6436</v>
+        <v>1.6844</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.1296</v>
+        <v>-4.131</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.3268</v>
+        <v>-6.885</v>
       </c>
       <c r="R9" t="n">
-        <v>4.1972</v>
+        <v>2.754</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.2647</v>
+        <v>-2.175</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.2375</v>
+        <v>-1.1214</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0272</v>
+        <v>-1.0536</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4246</v>
+        <v>-0.9937</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4246</v>
+        <v>-0.9937</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.9289</v>
+        <v>-7.8692</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2529</v>
+        <v>-1.5788</v>
       </c>
       <c r="F10" t="n">
-        <v>-16.1818</v>
+        <v>-6.2904</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.8919</v>
+        <v>-7.759399999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-13.7125</v>
+        <v>-9.146800000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8205</v>
+        <v>1.3876</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6825</v>
+        <v>-0.7671000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.3627</v>
+        <v>-5.1048</v>
       </c>
       <c r="L10" t="n">
-        <v>8.0449</v>
+        <v>4.3377</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.5744</v>
+        <v>-6.9922</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.3498</v>
+        <v>-4.042</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.2246</v>
+        <v>-2.9503</v>
       </c>
       <c r="P10" t="n">
-        <v>9.326499999999999</v>
+        <v>0.4590000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0985</v>
+        <v>-2.754</v>
       </c>
       <c r="R10" t="n">
-        <v>11.425</v>
+        <v>3.213</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.2851</v>
+        <v>-2.7332</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.4914</v>
+        <v>-1.304</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7937</v>
+        <v>-1.4292</v>
       </c>
       <c r="V10" t="n">
-        <v>-10.0786</v>
+        <v>2.164</v>
       </c>
       <c r="W10" t="n">
-        <v>6.160399999999999</v>
+        <v>3.246</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.2387</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="11">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.7394</v>
+        <v>-7.8902</v>
       </c>
       <c r="E11" t="n">
-        <v>13.2081</v>
+        <v>3.9766</v>
       </c>
       <c r="F11" t="n">
-        <v>-26.9472</v>
+        <v>-11.8665</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7639</v>
+        <v>1.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8379999999999999</v>
+        <v>1.4501</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9253</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>23.8475</v>
+        <v>9.5068</v>
       </c>
       <c r="K11" t="n">
-        <v>13.6676</v>
+        <v>5.7418</v>
       </c>
       <c r="L11" t="n">
-        <v>10.1798</v>
+        <v>3.765</v>
       </c>
       <c r="M11" t="n">
-        <v>-20.0838</v>
+        <v>-7.7067</v>
       </c>
       <c r="N11" t="n">
-        <v>-12.8293</v>
+        <v>-4.2919</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.2545</v>
+        <v>-3.415</v>
       </c>
       <c r="P11" t="n">
-        <v>7.694199999999999</v>
+        <v>0.918</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.9279</v>
+        <v>-4.59</v>
       </c>
       <c r="R11" t="n">
-        <v>15.6221</v>
+        <v>5.508</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.9676</v>
+        <v>-3.3616</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.981400000000001</v>
+        <v>-2.0223</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9865000000000002</v>
+        <v>-1.3391</v>
       </c>
       <c r="V11" t="n">
-        <v>-17.2303</v>
+        <v>-7.2463</v>
       </c>
       <c r="W11" t="n">
-        <v>4.2695</v>
+        <v>1.082</v>
       </c>
       <c r="X11" t="n">
-        <v>-21.4998</v>
+        <v>-8.3285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. YEBO</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.891</v>
+        <v>-9.7218</v>
       </c>
       <c r="E12" t="n">
-        <v>2.843800000000001</v>
+        <v>-1.5177</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.7346</v>
+        <v>-8.2044</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0352</v>
+        <v>-4.1971</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.7623</v>
+        <v>-3.3989</v>
       </c>
       <c r="I12" t="n">
-        <v>5.727099999999999</v>
+        <v>-0.7983</v>
       </c>
       <c r="J12" t="n">
-        <v>13.5001</v>
+        <v>0.5779999999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>8.312500000000002</v>
+        <v>1.5517</v>
       </c>
       <c r="L12" t="n">
-        <v>5.1877</v>
+        <v>-0.9737</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.5353</v>
+        <v>-4.7749</v>
       </c>
       <c r="N12" t="n">
-        <v>-15.0745</v>
+        <v>-4.9504</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5394999999999999</v>
+        <v>0.1754999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4974</v>
+        <v>0.2295</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.2907</v>
+        <v>-1.6065</v>
       </c>
       <c r="R12" t="n">
-        <v>9.792999999999999</v>
+        <v>1.836</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.8659</v>
+        <v>-0.3442</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.4194</v>
+        <v>-0.489</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5534999999999999</v>
+        <v>0.1448</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.4923</v>
+        <v>-5.41</v>
       </c>
       <c r="W12" t="n">
-        <v>6.0542</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-14.5465</v>
+        <v>-5.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>K. YEBO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.0651</v>
+        <v>-10.2039</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8338999999999999</v>
+        <v>-3.0486</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.2315</v>
+        <v>-7.1555</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.2712</v>
+        <v>-6.015499999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.7724</v>
+        <v>-4.2676</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5012</v>
+        <v>-1.748</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5089</v>
+        <v>1.6764</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0184</v>
+        <v>1.6059</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4901999999999997</v>
+        <v>0.07040000000000024</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.7798</v>
+        <v>-7.692</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.7911</v>
+        <v>-5.8735</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0114000000000001</v>
+        <v>-1.8184</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3989</v>
+        <v>-1.836</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8654</v>
+        <v>-5.2785</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2643</v>
+        <v>3.4425</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5869</v>
+        <v>-1.4213</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4774</v>
+        <v>-0.6793999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8901999999999999</v>
+        <v>-0.742</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.606</v>
+        <v>-0.9311999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2329</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.606</v>
+        <v>-2.164</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-43.5496</v>
+        <v>-15.5242</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.1694</v>
+        <v>1.4043</v>
       </c>
       <c r="F14" t="n">
-        <v>-33.3799</v>
+        <v>-16.9285</v>
       </c>
       <c r="G14" t="n">
-        <v>-15.7098</v>
+        <v>-7.1488</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.5672</v>
+        <v>-6.6903</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.1432</v>
+        <v>-0.4584999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0164</v>
+        <v>1.8717</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4601000000000002</v>
+        <v>-0.1346999999999996</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4763</v>
+        <v>2.0066</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.7265</v>
+        <v>-9.0206</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.1066</v>
+        <v>-6.5556</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.6195</v>
+        <v>-2.4652</v>
       </c>
       <c r="P14" t="n">
-        <v>-14.9228</v>
+        <v>-2.9835</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.6536</v>
+        <v>-4.8195</v>
       </c>
       <c r="R14" t="n">
-        <v>3.7308</v>
+        <v>1.836</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.5435</v>
+        <v>-2.9886</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.221</v>
+        <v>-0.8189000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.3222</v>
+        <v>-2.1697</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.373499999999999</v>
+        <v>-2.4032</v>
       </c>
       <c r="W14" t="n">
-        <v>10.6885</v>
+        <v>5.1708</v>
       </c>
       <c r="X14" t="n">
-        <v>-17.0621</v>
+        <v>-7.574</v>
       </c>
     </row>
     <row r="15">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-106.2355</v>
+        <v>-59.31339999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>41.8252</v>
+        <v>6.477200000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-148.0602</v>
+        <v>-65.7906</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.4821</v>
+        <v>-26.1721</v>
       </c>
       <c r="H15" t="n">
-        <v>-88.483</v>
+        <v>-43.2144</v>
       </c>
       <c r="I15" t="n">
-        <v>77.99989999999998</v>
+        <v>17.0423</v>
       </c>
       <c r="J15" t="n">
-        <v>129.084</v>
+        <v>38.4862</v>
       </c>
       <c r="K15" t="n">
-        <v>30.3211</v>
+        <v>5.010800000000002</v>
       </c>
       <c r="L15" t="n">
-        <v>98.7624</v>
+        <v>33.4756</v>
       </c>
       <c r="M15" t="n">
-        <v>-139.5665</v>
+        <v>-64.658</v>
       </c>
       <c r="N15" t="n">
-        <v>-118.803</v>
+        <v>-48.22479999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-20.7625</v>
+        <v>-16.433</v>
       </c>
       <c r="P15" t="n">
-        <v>-20.9858</v>
+        <v>-4.590000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-125.9113</v>
+        <v>-43.60489999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>104.9255</v>
+        <v>39.015</v>
       </c>
       <c r="S15" t="n">
-        <v>-45.73589999999999</v>
+        <v>-22.7149</v>
       </c>
       <c r="T15" t="n">
-        <v>-41.00370000000001</v>
+        <v>-13.7175</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.733400000000001</v>
+        <v>-8.9971</v>
       </c>
       <c r="V15" t="n">
-        <v>-29.0326</v>
+        <v>-5.8366</v>
       </c>
       <c r="W15" t="n">
-        <v>79.6551</v>
+        <v>25.3129</v>
       </c>
       <c r="X15" t="n">
-        <v>-108.688</v>
+        <v>-31.1497</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9383</v>
+        <v>4.0909</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9197</v>
+        <v>7.3615</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.9813</v>
+        <v>-3.2706</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8523</v>
+        <v>5.6376</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.5804</v>
+        <v>-3.6437</v>
       </c>
       <c r="I2" t="n">
-        <v>5.432600000000001</v>
+        <v>9.281499999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>13.0348</v>
+        <v>15.9521</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5704</v>
+        <v>4.6174</v>
       </c>
       <c r="L2" t="n">
-        <v>10.4644</v>
+        <v>11.3347</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.182699999999999</v>
+        <v>-10.3144</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.1507</v>
+        <v>-8.261099999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-5.0318</v>
+        <v>-2.0531</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.59</v>
+        <v>4.6796</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7.1145</v>
+        <v>-6.0833</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5245</v>
+        <v>10.7625</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7341</v>
+        <v>-4.2551</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0145</v>
+        <v>-2.5074</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2802999999999999</v>
+        <v>-1.7477</v>
       </c>
       <c r="V2" t="n">
-        <v>5.4101</v>
+        <v>-1.9712</v>
       </c>
       <c r="W2" t="n">
-        <v>6.013500000000001</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6034</v>
+        <v>-1.9712</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9922</v>
+        <v>4.0467</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1037</v>
+        <v>4.0385</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1115</v>
+        <v>0.008199999999999985</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6443</v>
+        <v>1.2762</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.4262</v>
+        <v>1.4479</v>
       </c>
       <c r="I3" t="n">
-        <v>8.070500000000001</v>
+        <v>-0.1718000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>8.1957</v>
+        <v>2.6878</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7589000000000001</v>
+        <v>1.2237</v>
       </c>
       <c r="L3" t="n">
-        <v>7.4368</v>
+        <v>1.4641</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.5512</v>
+        <v>-1.4116</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.185</v>
+        <v>0.2242999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6337999999999999</v>
+        <v>-1.6359</v>
       </c>
       <c r="P3" t="n">
-        <v>3.9015</v>
+        <v>-0.234</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9834</v>
+        <v>-1.6378</v>
       </c>
       <c r="R3" t="n">
-        <v>6.885</v>
+        <v>1.4038</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.17</v>
+        <v>-0.8717000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.1085</v>
+        <v>-0.2037</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0614</v>
+        <v>-0.6679999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.3838</v>
+        <v>3.8763</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.1924</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3838</v>
+        <v>0.6839</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>D. BORDON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.328</v>
+        <v>-0.284</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9975000000000001</v>
+        <v>-0.5904</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3305</v>
+        <v>0.3065</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5426</v>
+        <v>-1.4463</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8761</v>
+        <v>-1.1231</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3335</v>
+        <v>-0.3232</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6338</v>
+        <v>-1.5988</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5968</v>
+        <v>-0.7911</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0371</v>
+        <v>-0.8077</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0912</v>
+        <v>0.1525</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2793</v>
+        <v>-0.3321</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3705</v>
+        <v>0.4845</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.234</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.234</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5359</v>
+        <v>-0.0014</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1773</v>
+        <v>-0.0558</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3586</v>
+        <v>0.0543</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3213</v>
+        <v>0.9298</v>
       </c>
       <c r="W4" t="n">
-        <v>0.541</v>
+        <v>1.0641</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7803</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1196</v>
+        <v>-1.1443</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8428</v>
+        <v>0.5717000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7232000000000002</v>
+        <v>-1.7157</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6077000000000004</v>
+        <v>-2.2389</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2922</v>
+        <v>-3.2519</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.0131</v>
       </c>
       <c r="J5" t="n">
-        <v>3.216</v>
+        <v>2.483</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5857</v>
+        <v>1.6437</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6303</v>
+        <v>0.8395000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6082</v>
+        <v>-4.722</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.8779</v>
+        <v>-4.8956</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2697000000000001</v>
+        <v>0.1735999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1.377</v>
+        <v>2.5738</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.459</v>
+        <v>-0.468</v>
       </c>
       <c r="R5" t="n">
-        <v>1.836</v>
+        <v>3.0418</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5633</v>
+        <v>-1.2103</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9141</v>
+        <v>-1.4435</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3508</v>
+        <v>0.2331000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3018</v>
+        <v>-0.2686</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>-0.2686</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. BORDON</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.286</v>
+        <v>-2.074199999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5596</v>
+        <v>7.801200000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2736</v>
+        <v>-9.875299999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4558</v>
+        <v>-1.1906</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1324</v>
+        <v>-3.4062</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3234</v>
+        <v>2.215599999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5998</v>
+        <v>11.3937</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7914</v>
+        <v>1.5792</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8084</v>
+        <v>9.814500000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1441</v>
+        <v>-12.5843</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.341</v>
+        <v>-4.9855</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4851</v>
+        <v>-7.5989</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2295</v>
+        <v>-5.381399999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-9.1249</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2295</v>
+        <v>3.7435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0091</v>
+        <v>-1.142</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0417</v>
+        <v>-1.3896</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0509</v>
+        <v>0.2474</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9312</v>
+        <v>5.6397</v>
       </c>
       <c r="W6" t="n">
-        <v>1.082</v>
+        <v>6.9218</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1509</v>
+        <v>-1.2821</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.1338</v>
+        <v>-5.2836</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5421999999999998</v>
+        <v>0.4226000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.676</v>
+        <v>-5.7062</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.9451</v>
+        <v>-1.7977</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.2825</v>
+        <v>-4.0161</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3372</v>
+        <v>2.2184</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3492</v>
+        <v>7.7491</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.5252</v>
+        <v>1.3778</v>
       </c>
       <c r="L7" t="n">
-        <v>3.176</v>
+        <v>6.371499999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.5961</v>
+        <v>-9.547000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.7573</v>
+        <v>-5.393800000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8388</v>
+        <v>-4.1532</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9835</v>
+        <v>-3.5095</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.377</v>
+        <v>-10.9968</v>
       </c>
       <c r="R7" t="n">
-        <v>4.3605</v>
+        <v>7.486899999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0967</v>
+        <v>-3.1965</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3613</v>
+        <v>-1.9191</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-1.2774</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9248</v>
+        <v>3.2202</v>
       </c>
       <c r="W7" t="n">
-        <v>4.6298</v>
+        <v>5.5891</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.705</v>
+        <v>-2.3689</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.4996</v>
+        <v>-9.388199999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1145</v>
+        <v>-3.8605</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.385</v>
+        <v>-5.5278</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.834</v>
+        <v>-12.1341</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.1575</v>
+        <v>-13.2625</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3235</v>
+        <v>1.1283</v>
       </c>
       <c r="J8" t="n">
-        <v>1.973200000000001</v>
+        <v>-5.468</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1421</v>
+        <v>-8.672000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>3.1152</v>
+        <v>3.204</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.8072</v>
+        <v>-6.6662</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.015499999999999</v>
+        <v>-4.5905</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7915</v>
+        <v>-2.0757</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1475</v>
+        <v>3.2757</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.7375</v>
+        <v>-3.5095</v>
       </c>
       <c r="R8" t="n">
-        <v>4.59</v>
+        <v>6.7852</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.6001</v>
+        <v>-3.1115</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.6651</v>
+        <v>-1.5363</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9349000000000001</v>
+        <v>-1.5752</v>
       </c>
       <c r="V8" t="n">
-        <v>1.082</v>
+        <v>2.5817</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3149</v>
+        <v>6.6532</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2329</v>
+        <v>-4.0715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. FRIDRIKSSON</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.5628</v>
+        <v>-9.7767</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.490399999999999</v>
+        <v>-2.3584</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.07239999999999991</v>
+        <v>-7.4181</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7367000000000001</v>
+        <v>-4.4836</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1657999999999999</v>
+        <v>-3.0131</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9026</v>
+        <v>-1.4705</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5159</v>
+        <v>0.7676999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>2.297800000000001</v>
+        <v>2.5734</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7817999999999999</v>
+        <v>-1.8058</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7791000000000001</v>
+        <v>-5.251300000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.4633</v>
+        <v>-5.5868</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6844</v>
+        <v>0.3351999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.131</v>
+        <v>0.2338999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.885</v>
+        <v>-2.8078</v>
       </c>
       <c r="R9" t="n">
-        <v>2.754</v>
+        <v>3.0417</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.175</v>
+        <v>-0.2065</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1214</v>
+        <v>-0.3183999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0536</v>
+        <v>0.1119999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9937</v>
+        <v>-5.3205</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9937</v>
+        <v>-5.3205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>E. FRIDRIKSSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.8692</v>
+        <v>-10.2813</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5788</v>
+        <v>-10.1188</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.2904</v>
+        <v>-0.1625000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.759399999999999</v>
+        <v>-0.7575000000000003</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.146800000000001</v>
+        <v>-2.0705</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3876</v>
+        <v>1.3128</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7671000000000001</v>
+        <v>0.4554</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.1048</v>
+        <v>0.9093000000000002</v>
       </c>
       <c r="L10" t="n">
-        <v>4.3377</v>
+        <v>-0.4537</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.9922</v>
+        <v>-1.2129</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.042</v>
+        <v>-2.9795</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.9503</v>
+        <v>1.7666</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4590000000000001</v>
+        <v>-5.8492</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.754</v>
+        <v>-9.3588</v>
       </c>
       <c r="R10" t="n">
-        <v>3.213</v>
+        <v>3.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.7332</v>
+        <v>-2.7396</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.304</v>
+        <v>-1.2152</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4292</v>
+        <v>-1.5244</v>
       </c>
       <c r="V10" t="n">
-        <v>2.164</v>
+        <v>-0.9349999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>3.246</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.082</v>
+        <v>-0.9349999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.8902</v>
+        <v>-15.571</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9766</v>
+        <v>-5.9688</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.8665</v>
+        <v>-9.602599999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8</v>
+        <v>-11.1808</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4501</v>
+        <v>-12.1666</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3500000000000001</v>
+        <v>0.9859000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>9.5068</v>
+        <v>-1.0531</v>
       </c>
       <c r="K11" t="n">
-        <v>5.7418</v>
+        <v>-6.633700000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>3.765</v>
+        <v>5.5807</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.7067</v>
+        <v>-10.1277</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.2919</v>
+        <v>-5.5331</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.415</v>
+        <v>-4.594799999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0.918</v>
+        <v>-2.1058</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.59</v>
+        <v>-7.9551</v>
       </c>
       <c r="R11" t="n">
-        <v>5.508</v>
+        <v>5.849299999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.3616</v>
+        <v>-4.8386</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.0223</v>
+        <v>-2.2813</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3391</v>
+        <v>-2.5573</v>
       </c>
       <c r="V11" t="n">
-        <v>-7.2463</v>
+        <v>2.5539</v>
       </c>
       <c r="W11" t="n">
-        <v>1.082</v>
+        <v>5.3205</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.3285</v>
+        <v>-2.7668</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.7218</v>
+        <v>-16.0129</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5177</v>
+        <v>2.0719</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.2044</v>
+        <v>-18.0848</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1971</v>
+        <v>-4.4837</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.3989</v>
+        <v>2.3516</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7983</v>
+        <v>-6.8355</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5779999999999998</v>
+        <v>7.886299999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5517</v>
+        <v>7.9205</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9737</v>
+        <v>-0.03420000000000023</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.7749</v>
+        <v>-12.3701</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.9504</v>
+        <v>-5.5689</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1754999999999999</v>
+        <v>-6.8013</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2295</v>
+        <v>2.3396</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.6065</v>
+        <v>-4.9134</v>
       </c>
       <c r="R12" t="n">
-        <v>1.836</v>
+        <v>7.253</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3442</v>
+        <v>-4.0458</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.489</v>
+        <v>-3.0294</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1448</v>
+        <v>-1.0167</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.41</v>
+        <v>-9.822900000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.1283</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.41</v>
+        <v>-11.951</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.2039</v>
+        <v>-16.0707</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0486</v>
+        <v>-4.8621</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.1555</v>
+        <v>-11.2087</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.015499999999999</v>
+        <v>-9.6075</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.2676</v>
+        <v>-4.6558</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.748</v>
+        <v>-4.9518</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6764</v>
+        <v>1.196</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6059</v>
+        <v>2.6404</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07040000000000024</v>
+        <v>-1.4446</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.692</v>
+        <v>-10.8036</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.8735</v>
+        <v>-7.2964</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8184</v>
+        <v>-3.5072</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.836</v>
+        <v>-1.8717</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.2785</v>
+        <v>-6.7852</v>
       </c>
       <c r="R13" t="n">
-        <v>3.4425</v>
+        <v>4.9135</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4213</v>
+        <v>-1.5335</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6793999999999999</v>
+        <v>-0.07349999999999987</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.742</v>
+        <v>-1.46</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9311999999999998</v>
+        <v>-3.0579</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2329</v>
+        <v>0.8007000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.164</v>
+        <v>-3.8587</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.5242</v>
+        <v>-21.6795</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4043</v>
+        <v>-1.443599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.9285</v>
+        <v>-20.236</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.1488</v>
+        <v>-12.8632</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.6903</v>
+        <v>-10.9856</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4584999999999999</v>
+        <v>-1.8776</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8717</v>
+        <v>-0.6422999999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1346999999999996</v>
+        <v>-2.509100000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0066</v>
+        <v>1.8668</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.0206</v>
+        <v>-12.2208</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.5556</v>
+        <v>-8.4765</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.4652</v>
+        <v>-3.7444</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.9835</v>
+        <v>-2.5738</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.8195</v>
+        <v>-5.3815</v>
       </c>
       <c r="R14" t="n">
-        <v>1.836</v>
+        <v>2.8077</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.9886</v>
+        <v>-3.879</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8189000000000001</v>
+        <v>-1.1433</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.1697</v>
+        <v>-2.7356</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.4032</v>
+        <v>-2.3638</v>
       </c>
       <c r="W14" t="n">
-        <v>5.1708</v>
+        <v>5.7235</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.574</v>
+        <v>-8.087400000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-59.31339999999999</v>
+        <v>-99.42880000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>6.477200000000001</v>
+        <v>-6.935199999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-65.7906</v>
+        <v>-92.4936</v>
       </c>
       <c r="G15" t="n">
-        <v>-26.1721</v>
+        <v>-55.2701</v>
       </c>
       <c r="H15" t="n">
-        <v>-43.2144</v>
+        <v>-57.79560000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>17.0423</v>
+        <v>2.525199999999998</v>
       </c>
       <c r="J15" t="n">
-        <v>38.4862</v>
+        <v>41.80889999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>5.010800000000002</v>
+        <v>5.879499999999997</v>
       </c>
       <c r="L15" t="n">
-        <v>33.4756</v>
+        <v>35.92979999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-64.658</v>
+        <v>-97.07940000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-48.22479999999999</v>
+        <v>-63.6755</v>
       </c>
       <c r="O15" t="n">
-        <v>-16.433</v>
+        <v>-33.4046</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.590000000000001</v>
+        <v>-8.188799999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-43.60489999999999</v>
+        <v>-69.02210000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>39.015</v>
+        <v>60.83249999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-22.7149</v>
+        <v>-31.0315</v>
       </c>
       <c r="T15" t="n">
-        <v>-13.7175</v>
+        <v>-17.1165</v>
       </c>
       <c r="U15" t="n">
-        <v>-8.9971</v>
+        <v>-13.9155</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.8366</v>
+        <v>-4.938300000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>25.3129</v>
+        <v>37.39359999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-31.1497</v>
+        <v>-42.3321</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
@@ -565,73 +565,73 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0909</v>
+        <v>1.6451</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3615</v>
+        <v>6.067099999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.2706</v>
+        <v>-4.4221</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6376</v>
+        <v>3.6989</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.6437</v>
+        <v>-3.9749</v>
       </c>
       <c r="I2" t="n">
-        <v>9.281499999999999</v>
+        <v>7.6738</v>
       </c>
       <c r="J2" t="n">
-        <v>15.9521</v>
+        <v>12.6061</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6174</v>
+        <v>3.6931</v>
       </c>
       <c r="L2" t="n">
-        <v>11.3347</v>
+        <v>8.913</v>
       </c>
       <c r="M2" t="n">
-        <v>-10.3144</v>
+        <v>-8.907299999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-8.261099999999999</v>
+        <v>-7.668</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0531</v>
+        <v>-1.2392</v>
       </c>
       <c r="P2" t="n">
-        <v>4.6796</v>
+        <v>5.3377</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.0833</v>
+        <v>-4.4094</v>
       </c>
       <c r="R2" t="n">
-        <v>10.7625</v>
+        <v>9.7469</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.2551</v>
+        <v>-2.8561</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.5074</v>
+        <v>-2.1296</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.7477</v>
+        <v>-0.7264999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.9712</v>
+        <v>-4.5353</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.9712</v>
+        <v>-4.5353</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0467</v>
+        <v>-0.2944999999999993</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0385</v>
+        <v>6.851699999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008199999999999985</v>
+        <v>-7.146</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2762</v>
+        <v>2.5189</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4479</v>
+        <v>-1.6432</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1718000000000001</v>
+        <v>4.1619</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6878</v>
+        <v>12.536</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2237</v>
+        <v>4.9711</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4641</v>
+        <v>7.565</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4116</v>
+        <v>-10.0172</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2242999999999999</v>
+        <v>-6.6139</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6359</v>
+        <v>-3.4032</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.234</v>
+        <v>-7.4262</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6378</v>
+        <v>-14.8527</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4038</v>
+        <v>7.426200000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8717000000000001</v>
+        <v>-2.358</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2037</v>
+        <v>-1.6903</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6679999999999999</v>
+        <v>-0.6677000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8763</v>
+        <v>6.970800000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1924</v>
+        <v>10.8584</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6839</v>
+        <v>-3.8876</v>
       </c>
     </row>
     <row r="4">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.284</v>
+        <v>-0.4543</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5904</v>
+        <v>-0.5874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3065</v>
+        <v>0.1331</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4463</v>
+        <v>-1.6252</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1231</v>
+        <v>-1.1354</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3232</v>
+        <v>-0.4898</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.5988</v>
+        <v>-1.6159</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7911</v>
+        <v>-0.7996</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8077</v>
+        <v>-0.8164</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1525</v>
+        <v>-0.009300000000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3321</v>
+        <v>-0.3359</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4845</v>
+        <v>0.3266</v>
       </c>
       <c r="P4" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0014</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0558</v>
+        <v>-0.0431</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0543</v>
+        <v>0.0516</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9298</v>
+        <v>0.9304</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SASTRE</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1443</v>
+        <v>-2.4564</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5717000000000001</v>
+        <v>0.4530000000000003</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7157</v>
+        <v>-2.9094</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2389</v>
+        <v>-0.1137</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.2519</v>
+        <v>0.01960000000000006</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0131</v>
+        <v>-0.1333</v>
       </c>
       <c r="J5" t="n">
-        <v>2.483</v>
+        <v>2.1758</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6437</v>
+        <v>0.6304</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8395000000000001</v>
+        <v>1.5453</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.722</v>
+        <v>-2.2895</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.8956</v>
+        <v>-0.6108</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1735999999999999</v>
+        <v>-1.6786</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5738</v>
+        <v>-1.8566</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.468</v>
+        <v>-4.1773</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0418</v>
+        <v>2.3207</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2103</v>
+        <v>-0.8854</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4435</v>
+        <v>-0.2248</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2331000000000001</v>
+        <v>-0.6606000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2686</v>
+        <v>0.3991999999999996</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.6793</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2686</v>
+        <v>-2.2801</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>J. SASTRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.074199999999999</v>
+        <v>-3.8499</v>
       </c>
       <c r="E6" t="n">
-        <v>7.801200000000001</v>
+        <v>-2.362</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.875299999999999</v>
+        <v>-1.4878</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1906</v>
+        <v>-3.9444</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.4062</v>
+        <v>-1.8012</v>
       </c>
       <c r="I6" t="n">
-        <v>2.215599999999999</v>
+        <v>-2.1431</v>
       </c>
       <c r="J6" t="n">
-        <v>11.3937</v>
+        <v>-0.05819999999999981</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5792</v>
+        <v>1.6691</v>
       </c>
       <c r="L6" t="n">
-        <v>9.814500000000001</v>
+        <v>-1.7272</v>
       </c>
       <c r="M6" t="n">
-        <v>-12.5843</v>
+        <v>-3.8863</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.9855</v>
+        <v>-3.4703</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.5989</v>
+        <v>-0.4159999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-5.381399999999999</v>
+        <v>2.0887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-9.1249</v>
+        <v>-1.6246</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7435</v>
+        <v>3.7133</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.142</v>
+        <v>-0.2452000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3896</v>
+        <v>-1.7512</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2474</v>
+        <v>1.506</v>
       </c>
       <c r="V6" t="n">
-        <v>5.6397</v>
+        <v>-1.7489</v>
       </c>
       <c r="W6" t="n">
-        <v>6.9218</v>
+        <v>1.0717</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2821</v>
+        <v>-2.8206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.2836</v>
+        <v>-5.529500000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4226000000000001</v>
+        <v>-0.6784</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.7062</v>
+        <v>-4.851</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7977</v>
+        <v>-2.69</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.0161</v>
+        <v>-2.3704</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2184</v>
+        <v>-0.3196</v>
       </c>
       <c r="J7" t="n">
-        <v>7.7491</v>
+        <v>1.0787</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3778</v>
+        <v>1.3937</v>
       </c>
       <c r="L7" t="n">
-        <v>6.371499999999999</v>
+        <v>-0.3150999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-9.547000000000001</v>
+        <v>-3.7687</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.393800000000001</v>
+        <v>-3.7643</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.1532</v>
+        <v>-0.004399999999999973</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.5095</v>
+        <v>0.4641000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-10.9968</v>
+        <v>-1.3925</v>
       </c>
       <c r="R7" t="n">
-        <v>7.486899999999999</v>
+        <v>1.8566</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.1965</v>
+        <v>-0.0885</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.9191</v>
+        <v>-0.3647</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2774</v>
+        <v>0.2762</v>
       </c>
       <c r="V7" t="n">
-        <v>3.2202</v>
+        <v>-3.215100000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>5.5891</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3689</v>
+        <v>-3.215100000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>E. FRIDRIKSSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.388199999999999</v>
+        <v>-6.5464</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.8605</v>
+        <v>-6.052200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.5278</v>
+        <v>-0.4942000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-12.1341</v>
+        <v>-1.5203</v>
       </c>
       <c r="H8" t="n">
-        <v>-13.2625</v>
+        <v>-2.017</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1283</v>
+        <v>0.4966</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.468</v>
+        <v>-0.6402000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.672000000000001</v>
+        <v>0.08659999999999979</v>
       </c>
       <c r="L8" t="n">
-        <v>3.204</v>
+        <v>-0.7268</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.6662</v>
+        <v>-0.8802</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.5905</v>
+        <v>-2.1036</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0757</v>
+        <v>1.2234</v>
       </c>
       <c r="P8" t="n">
-        <v>3.2757</v>
+        <v>-2.7848</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.5095</v>
+        <v>-4.6414</v>
       </c>
       <c r="R8" t="n">
-        <v>6.7852</v>
+        <v>1.8566</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.1115</v>
+        <v>-1.4228</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5363</v>
+        <v>-0.7706000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.5752</v>
+        <v>-0.6522000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5817</v>
+        <v>-0.8185</v>
       </c>
       <c r="W8" t="n">
-        <v>6.6532</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.0715</v>
+        <v>-0.8185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.7767</v>
+        <v>-6.905399999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3584</v>
+        <v>5.867</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.4181</v>
+        <v>-12.7725</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4836</v>
+        <v>-1.2889</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0131</v>
+        <v>-0.1665</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4705</v>
+        <v>-1.1223</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7676999999999999</v>
+        <v>10.6255</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5734</v>
+        <v>5.645</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8058</v>
+        <v>4.9804</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.251300000000001</v>
+        <v>-11.9143</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.5868</v>
+        <v>-5.811599999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3351999999999999</v>
+        <v>-6.1027</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2338999999999999</v>
+        <v>4.1772</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8078</v>
+        <v>-3.9453</v>
       </c>
       <c r="R9" t="n">
-        <v>3.0417</v>
+        <v>8.122400000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2065</v>
+        <v>-2.9442</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3183999999999999</v>
+        <v>-2.9567</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1119999999999999</v>
+        <v>0.01239999999999998</v>
       </c>
       <c r="V9" t="n">
-        <v>-5.3205</v>
+        <v>-6.849600000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.1435</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.3205</v>
+        <v>-8.993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. FRIDRIKSSON</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.2813</v>
+        <v>-7.105499999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.1188</v>
+        <v>1.1683</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1625000000000001</v>
+        <v>-8.2738</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7575000000000003</v>
+        <v>-4.128200000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0705</v>
+        <v>-2.9622</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3128</v>
+        <v>-1.166000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4554</v>
+        <v>6.161300000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9093000000000002</v>
+        <v>1.4315</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4537</v>
+        <v>4.729899999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2129</v>
+        <v>-10.2896</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.9795</v>
+        <v>-4.3936</v>
       </c>
       <c r="O10" t="n">
-        <v>1.7666</v>
+        <v>-5.8958</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.8492</v>
+        <v>-2.0886</v>
       </c>
       <c r="Q10" t="n">
-        <v>-9.3588</v>
+        <v>-7.8905</v>
       </c>
       <c r="R10" t="n">
-        <v>3.5096</v>
+        <v>5.8017</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.7396</v>
+        <v>-1.9215</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2152</v>
+        <v>-2.096</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5244</v>
+        <v>0.1746</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9349999999999999</v>
+        <v>1.0329</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>4.993600000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9349999999999999</v>
+        <v>-3.9607</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.571</v>
+        <v>-7.3685</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9688</v>
+        <v>-0.6789000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.602599999999999</v>
+        <v>-6.6896</v>
       </c>
       <c r="G11" t="n">
-        <v>-11.1808</v>
+        <v>-6.93</v>
       </c>
       <c r="H11" t="n">
-        <v>-12.1666</v>
+        <v>-7.097799999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9859000000000001</v>
+        <v>0.1679999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0531</v>
+        <v>-1.0342</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.633700000000001</v>
+        <v>-3.1335</v>
       </c>
       <c r="L11" t="n">
-        <v>5.5807</v>
+        <v>2.0993</v>
       </c>
       <c r="M11" t="n">
-        <v>-10.1277</v>
+        <v>-5.8958</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.5331</v>
+        <v>-3.9643</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.594799999999999</v>
+        <v>-1.9314</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1058</v>
+        <v>4.873600000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.9551</v>
+        <v>-2.5527</v>
       </c>
       <c r="R11" t="n">
-        <v>5.849299999999999</v>
+        <v>7.4263</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.8386</v>
+        <v>-1.7755</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.2813</v>
+        <v>-1.1255</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.5573</v>
+        <v>-0.6496999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>2.5539</v>
+        <v>-3.5367</v>
       </c>
       <c r="W11" t="n">
-        <v>5.3205</v>
+        <v>4.033600000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7668</v>
+        <v>-7.5704</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.0129</v>
+        <v>-8.8345</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0719</v>
+        <v>-4.159999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.0848</v>
+        <v>-4.6745</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.4837</v>
+        <v>-2.1221</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3516</v>
+        <v>-8.277699999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.8355</v>
+        <v>6.1558</v>
       </c>
       <c r="J12" t="n">
-        <v>7.886299999999999</v>
+        <v>6.979699999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>7.9205</v>
+        <v>-2.9885</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.03420000000000023</v>
+        <v>9.9682</v>
       </c>
       <c r="M12" t="n">
-        <v>-12.3701</v>
+        <v>-9.101599999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.5689</v>
+        <v>-5.289099999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.8013</v>
+        <v>-3.8124</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3396</v>
+        <v>-4.641500000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.9134</v>
+        <v>-12.9961</v>
       </c>
       <c r="R12" t="n">
-        <v>7.253</v>
+        <v>8.3546</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.0458</v>
+        <v>-4.1416</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.0294</v>
+        <v>-2.5718</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0167</v>
+        <v>-1.5698</v>
       </c>
       <c r="V12" t="n">
-        <v>-9.822900000000001</v>
+        <v>2.0704</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1283</v>
+        <v>4.428100000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.951</v>
+        <v>-2.3578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.0707</v>
+        <v>-10.304</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8621</v>
+        <v>-0.7757000000000003</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.2087</v>
+        <v>-9.5281</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.6075</v>
+        <v>-6.8768</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.6558</v>
+        <v>-2.4916</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.9518</v>
+        <v>-4.3852</v>
       </c>
       <c r="J13" t="n">
-        <v>1.196</v>
+        <v>2.123</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6404</v>
+        <v>3.7167</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.4446</v>
+        <v>-1.5938</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.8036</v>
+        <v>-8.999700000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.2964</v>
+        <v>-6.2084</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.5072</v>
+        <v>-2.7913</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8717</v>
+        <v>1.1604</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.7852</v>
+        <v>-5.569800000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>4.9135</v>
+        <v>6.7301</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5335</v>
+        <v>-0.7587</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.07349999999999987</v>
+        <v>-0.8563999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.46</v>
+        <v>0.09770000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.0579</v>
+        <v>-3.8286</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8007000000000001</v>
+        <v>3.5273</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.8587</v>
+        <v>-7.3559</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.6795</v>
+        <v>-15.3083</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.443599999999999</v>
+        <v>-2.264600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.236</v>
+        <v>-13.0438</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.8632</v>
+        <v>-7.1716</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.9856</v>
+        <v>-4.425799999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8776</v>
+        <v>-2.7459</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6422999999999998</v>
+        <v>1.4896</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.509100000000001</v>
+        <v>0.4251999999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8668</v>
+        <v>1.0643</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.2208</v>
+        <v>-8.661199999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.4765</v>
+        <v>-4.8509</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7444</v>
+        <v>-3.8102</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.5738</v>
+        <v>-4.1774</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.3815</v>
+        <v>-7.8905</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8077</v>
+        <v>3.7132</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.879</v>
+        <v>-3.3506</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1433</v>
+        <v>-1.5048</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.7356</v>
+        <v>-1.8458</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.3638</v>
+        <v>-0.6089</v>
       </c>
       <c r="W14" t="n">
-        <v>5.7235</v>
+        <v>5.6413</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.087400000000001</v>
+        <v>-6.2502</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-99.42880000000001</v>
+        <v>-73.3121</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.935199999999999</v>
+        <v>2.847899999999997</v>
       </c>
       <c r="F15" t="n">
-        <v>-92.4936</v>
+        <v>-76.1597</v>
       </c>
       <c r="G15" t="n">
-        <v>-55.2701</v>
+        <v>-32.1934</v>
       </c>
       <c r="H15" t="n">
-        <v>-57.79560000000001</v>
+        <v>-38.3441</v>
       </c>
       <c r="I15" t="n">
-        <v>2.525199999999998</v>
+        <v>6.150899999999995</v>
       </c>
       <c r="J15" t="n">
-        <v>41.80889999999999</v>
+        <v>52.42720000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>5.879499999999997</v>
+        <v>16.7408</v>
       </c>
       <c r="L15" t="n">
-        <v>35.92979999999999</v>
+        <v>35.6861</v>
       </c>
       <c r="M15" t="n">
-        <v>-97.07940000000001</v>
+        <v>-84.6207</v>
       </c>
       <c r="N15" t="n">
-        <v>-63.6755</v>
+        <v>-55.0847</v>
       </c>
       <c r="O15" t="n">
-        <v>-33.4046</v>
+        <v>-29.5352</v>
       </c>
       <c r="P15" t="n">
-        <v>-8.188799999999999</v>
+        <v>-4.641300000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-69.02210000000001</v>
+        <v>-71.94280000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>60.83249999999999</v>
+        <v>67.30070000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>-31.0315</v>
+        <v>-22.7396</v>
       </c>
       <c r="T15" t="n">
-        <v>-17.1165</v>
+        <v>-18.0855</v>
       </c>
       <c r="U15" t="n">
-        <v>-13.9155</v>
+        <v>-4.6538</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.938300000000001</v>
+        <v>-13.7379</v>
       </c>
       <c r="W15" t="n">
-        <v>37.39359999999999</v>
+        <v>40.4485</v>
       </c>
       <c r="X15" t="n">
-        <v>-42.3321</v>
+        <v>-54.1865</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
@@ -565,73 +565,73 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6451</v>
+        <v>1.8948</v>
       </c>
       <c r="E2" t="n">
-        <v>6.067099999999999</v>
+        <v>5.8661</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.4221</v>
+        <v>-3.9711</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6989</v>
+        <v>3.8915</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.9749</v>
+        <v>-3.820399999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6738</v>
+        <v>7.7119</v>
       </c>
       <c r="J2" t="n">
-        <v>12.6061</v>
+        <v>12.3988</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6931</v>
+        <v>3.5742</v>
       </c>
       <c r="L2" t="n">
-        <v>8.913</v>
+        <v>8.8245</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.907299999999999</v>
+        <v>-8.507400000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.668</v>
+        <v>-7.3948</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.2392</v>
+        <v>-1.1124</v>
       </c>
       <c r="P2" t="n">
-        <v>5.3377</v>
+        <v>5.3766</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.4094</v>
+        <v>-4.4415</v>
       </c>
       <c r="R2" t="n">
-        <v>9.7469</v>
+        <v>9.818300000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.8561</v>
+        <v>-2.8719</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.1296</v>
+        <v>-2.0914</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7264999999999999</v>
+        <v>-0.7806</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.5353</v>
+        <v>-4.5014</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.5353</v>
+        <v>-4.5014</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>D. BORDON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2944999999999993</v>
+        <v>-0.4614</v>
       </c>
       <c r="E3" t="n">
-        <v>6.851699999999999</v>
+        <v>-0.6091</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.146</v>
+        <v>0.1477</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5189</v>
+        <v>-1.635</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6432</v>
+        <v>-1.1403</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1619</v>
+        <v>-0.4947</v>
       </c>
       <c r="J3" t="n">
-        <v>12.536</v>
+        <v>-1.6323</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9711</v>
+        <v>-0.8078</v>
       </c>
       <c r="L3" t="n">
-        <v>7.565</v>
+        <v>-0.8245</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.0172</v>
+        <v>-0.002700000000000008</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.6139</v>
+        <v>-0.3325</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.4032</v>
+        <v>0.3298</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.4262</v>
+        <v>0.2338</v>
       </c>
       <c r="Q3" t="n">
-        <v>-14.8527</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>7.426200000000001</v>
+        <v>0.2338</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.358</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.6903</v>
+        <v>-0.0417</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6677000000000001</v>
+        <v>0.0517</v>
       </c>
       <c r="V3" t="n">
-        <v>6.970800000000001</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>10.8584</v>
+        <v>1.0649</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.8876</v>
+        <v>-0.1351</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BORDON</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4543</v>
+        <v>-0.5561999999999996</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5874</v>
+        <v>6.187200000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1331</v>
+        <v>-6.7436</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6252</v>
+        <v>2.3488</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1354</v>
+        <v>-1.6755</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4898</v>
+        <v>4.0242</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.6159</v>
+        <v>12.0253</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7996</v>
+        <v>4.7085</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8164</v>
+        <v>7.3168</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.009300000000000003</v>
+        <v>-9.676600000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3359</v>
+        <v>-6.383999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3266</v>
+        <v>-3.2927</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2321</v>
+        <v>-7.480500000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-14.961</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2321</v>
+        <v>7.4805</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008500000000000001</v>
+        <v>-2.3673</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0431</v>
+        <v>-1.6615</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0516</v>
+        <v>-0.706</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9304</v>
+        <v>6.9428</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0717</v>
+        <v>10.7844</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1413</v>
+        <v>-3.8416</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.4564</v>
+        <v>-2.4224</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4530000000000003</v>
+        <v>0.3408000000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.9094</v>
+        <v>-2.7633</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1137</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01960000000000006</v>
+        <v>0.0293000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1333</v>
+        <v>-0.109</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1758</v>
+        <v>2.0969</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6304</v>
+        <v>0.5587</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5453</v>
+        <v>1.5382</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2895</v>
+        <v>-2.1767</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6108</v>
+        <v>-0.5296000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6786</v>
+        <v>-1.6472</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8566</v>
+        <v>-1.8702</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1773</v>
+        <v>-4.207800000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3207</v>
+        <v>2.3377</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8854</v>
+        <v>-0.8907</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2248</v>
+        <v>-0.2106</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6606000000000001</v>
+        <v>-0.6800999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3991999999999996</v>
+        <v>0.4181999999999997</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6793</v>
+        <v>2.6624</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2801</v>
+        <v>-2.2442</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.8499</v>
+        <v>-3.7182</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.362</v>
+        <v>-2.4536</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4878</v>
+        <v>-1.2648</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.9444</v>
+        <v>-3.8448</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8012</v>
+        <v>-1.7211</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1431</v>
+        <v>-2.1238</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.05819999999999981</v>
+        <v>-0.1426000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6691</v>
+        <v>1.6358</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.7272</v>
+        <v>-1.7784</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.8863</v>
+        <v>-3.7022</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.4703</v>
+        <v>-3.357</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4159999999999999</v>
+        <v>-0.3454</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0887</v>
+        <v>2.1039</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6246</v>
+        <v>-1.6364</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7133</v>
+        <v>3.7403</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2452000000000001</v>
+        <v>-0.2445999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7512</v>
+        <v>-1.7394</v>
       </c>
       <c r="U6" t="n">
-        <v>1.506</v>
+        <v>1.4946</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7489</v>
+        <v>-1.7325</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0717</v>
+        <v>1.0649</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.8206</v>
+        <v>-2.7974</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.529500000000001</v>
+        <v>-5.4198</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6784</v>
+        <v>-0.721</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.851</v>
+        <v>-4.6989</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.69</v>
+        <v>-2.6086</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3704</v>
+        <v>-2.2975</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3196</v>
+        <v>-0.3110999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0787</v>
+        <v>1.0305</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3937</v>
+        <v>1.3797</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3150999999999999</v>
+        <v>-0.3493000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.7687</v>
+        <v>-3.639</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.7643</v>
+        <v>-3.6772</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.004399999999999973</v>
+        <v>0.03820000000000004</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4641000000000001</v>
+        <v>0.4675</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3925</v>
+        <v>-1.4026</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8566</v>
+        <v>1.8701</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0885</v>
+        <v>-0.0839</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3647</v>
+        <v>-0.3489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2762</v>
+        <v>0.2649</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.215100000000001</v>
+        <v>-3.1948</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.215100000000001</v>
+        <v>-3.1948</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.5464</v>
+        <v>-6.5467</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.052200000000001</v>
+        <v>-6.17</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4942000000000001</v>
+        <v>-0.3767</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5203</v>
+        <v>-1.5082</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.017</v>
+        <v>-1.9836</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4966</v>
+        <v>0.4755</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6402000000000001</v>
+        <v>-0.7342000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08659999999999979</v>
+        <v>0.03679999999999972</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7268</v>
+        <v>-0.7708000000000002</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8802</v>
+        <v>-0.774</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1036</v>
+        <v>-2.0203</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2234</v>
+        <v>1.2463</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7848</v>
+        <v>-2.8052</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.6414</v>
+        <v>-4.6754</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8566</v>
+        <v>1.8702</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4228</v>
+        <v>-1.4307</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7706000000000002</v>
+        <v>-0.7606000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6522000000000001</v>
+        <v>-0.6701</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8185</v>
+        <v>-0.8026</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8185</v>
+        <v>-0.8026</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.905399999999999</v>
+        <v>-6.725899999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>5.867</v>
+        <v>5.557700000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-12.7725</v>
+        <v>-12.2835</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2889</v>
+        <v>-1.1985</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1665</v>
+        <v>-0.02450000000000008</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1223</v>
+        <v>-1.1741</v>
       </c>
       <c r="J9" t="n">
-        <v>10.6255</v>
+        <v>10.3306</v>
       </c>
       <c r="K9" t="n">
-        <v>5.645</v>
+        <v>5.5392</v>
       </c>
       <c r="L9" t="n">
-        <v>4.9804</v>
+        <v>4.791499999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.9143</v>
+        <v>-11.5291</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.811599999999999</v>
+        <v>-5.5636</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.1027</v>
+        <v>-5.9656</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1772</v>
+        <v>4.2077</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9453</v>
+        <v>-3.9741</v>
       </c>
       <c r="R9" t="n">
-        <v>8.122400000000001</v>
+        <v>8.181800000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.9442</v>
+        <v>-2.9612</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.9567</v>
+        <v>-2.9288</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01239999999999998</v>
+        <v>-0.0323</v>
       </c>
       <c r="V9" t="n">
-        <v>-6.849600000000001</v>
+        <v>-6.7741</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1435</v>
+        <v>2.1299</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.993</v>
+        <v>-8.904</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.105499999999999</v>
+        <v>-7.222499999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1683</v>
+        <v>0.7051999999999996</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.2738</v>
+        <v>-7.9277</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.128200000000001</v>
+        <v>-4.2042</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9622</v>
+        <v>-2.9748</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.166000000000001</v>
+        <v>-1.2293</v>
       </c>
       <c r="J10" t="n">
-        <v>6.161300000000001</v>
+        <v>5.7913</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4315</v>
+        <v>1.2374</v>
       </c>
       <c r="L10" t="n">
-        <v>4.729899999999999</v>
+        <v>4.553900000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.2896</v>
+        <v>-9.9955</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.3936</v>
+        <v>-4.2122</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.8958</v>
+        <v>-5.7834</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0886</v>
+        <v>-2.1039</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.8905</v>
+        <v>-7.9482</v>
       </c>
       <c r="R10" t="n">
-        <v>5.8017</v>
+        <v>5.8442</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9215</v>
+        <v>-1.9302</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.096</v>
+        <v>-2.0732</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1746</v>
+        <v>0.1429999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0329</v>
+        <v>1.0154</v>
       </c>
       <c r="W10" t="n">
-        <v>4.993600000000001</v>
+        <v>4.9349</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.9607</v>
+        <v>-3.9195</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3685</v>
+        <v>-7.2503</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6789000000000001</v>
+        <v>-0.9600000000000004</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.6896</v>
+        <v>-6.2904</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.93</v>
+        <v>-6.8627</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.097799999999999</v>
+        <v>-7.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1679999999999999</v>
+        <v>0.2028000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0342</v>
+        <v>-1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.1335</v>
+        <v>-3.3304</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0993</v>
+        <v>2.0303</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.8958</v>
+        <v>-5.5625</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.9643</v>
+        <v>-3.7349</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9314</v>
+        <v>-1.8277</v>
       </c>
       <c r="P11" t="n">
-        <v>4.873600000000001</v>
+        <v>4.9091</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5527</v>
+        <v>-2.5714</v>
       </c>
       <c r="R11" t="n">
-        <v>7.4263</v>
+        <v>7.4805</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7755</v>
+        <v>-1.7823</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1255</v>
+        <v>-1.0858</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6496999999999999</v>
+        <v>-0.6966000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.5367</v>
+        <v>-3.5143</v>
       </c>
       <c r="W11" t="n">
-        <v>4.033600000000001</v>
+        <v>3.9975</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.5704</v>
+        <v>-7.5116</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.8345</v>
+        <v>-9.131599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.159999999999999</v>
+        <v>-4.830400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.6745</v>
+        <v>-4.300999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1221</v>
+        <v>-2.346</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.277699999999999</v>
+        <v>-8.442600000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>6.1558</v>
+        <v>6.0966</v>
       </c>
       <c r="J12" t="n">
-        <v>6.979699999999999</v>
+        <v>6.4089</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.9885</v>
+        <v>-3.383</v>
       </c>
       <c r="L12" t="n">
-        <v>9.9682</v>
+        <v>9.792</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.101599999999999</v>
+        <v>-8.7547</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.289099999999999</v>
+        <v>-5.0595</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.8124</v>
+        <v>-3.6952</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.641500000000001</v>
+        <v>-4.6754</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.9961</v>
+        <v>-13.0909</v>
       </c>
       <c r="R12" t="n">
-        <v>8.3546</v>
+        <v>8.415700000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.1416</v>
+        <v>-4.1623</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.5718</v>
+        <v>-2.5432</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5698</v>
+        <v>-1.619</v>
       </c>
       <c r="V12" t="n">
-        <v>2.0704</v>
+        <v>2.0519</v>
       </c>
       <c r="W12" t="n">
-        <v>4.428100000000001</v>
+        <v>4.3947</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3578</v>
+        <v>-2.3429</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.304</v>
+        <v>-10.4191</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7757000000000003</v>
+        <v>-1.2604</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.5281</v>
+        <v>-9.1587</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.8768</v>
+        <v>-7.0014</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4916</v>
+        <v>-2.6624</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.3852</v>
+        <v>-4.338900000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>2.123</v>
+        <v>1.6995</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7167</v>
+        <v>3.369</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5938</v>
+        <v>-1.6696</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.999700000000001</v>
+        <v>-8.700900000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.2084</v>
+        <v>-6.0315</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.7913</v>
+        <v>-2.6695</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1604</v>
+        <v>1.1689</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.569800000000001</v>
+        <v>-5.6105</v>
       </c>
       <c r="R13" t="n">
-        <v>6.7301</v>
+        <v>6.7792</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7587</v>
+        <v>-0.7607</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8563999999999998</v>
+        <v>-0.8223999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.09770000000000001</v>
+        <v>0.06160000000000004</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.8286</v>
+        <v>-3.8259</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5273</v>
+        <v>3.4728</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.3559</v>
+        <v>-7.2988</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.3083</v>
+        <v>-15.3458</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.264600000000001</v>
+        <v>-2.5824</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.0438</v>
+        <v>-12.7634</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.1716</v>
+        <v>-7.159899999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.425799999999999</v>
+        <v>-4.374499999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.7459</v>
+        <v>-2.7853</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4896</v>
+        <v>1.2519</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4251999999999998</v>
+        <v>0.3228</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0643</v>
+        <v>0.9290999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.661199999999999</v>
+        <v>-8.411899999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.8509</v>
+        <v>-4.6975</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.8102</v>
+        <v>-3.7143</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.1774</v>
+        <v>-4.2079</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.8905</v>
+        <v>-7.9481</v>
       </c>
       <c r="R14" t="n">
-        <v>3.7132</v>
+        <v>3.7403</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.3506</v>
+        <v>-3.3677</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5048</v>
+        <v>-1.481</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.8458</v>
+        <v>-1.8867</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6089</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>5.6413</v>
+        <v>5.5947</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.2502</v>
+        <v>-6.2052</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-73.3121</v>
+        <v>-73.32509999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.847899999999997</v>
+        <v>-0.9299000000000017</v>
       </c>
       <c r="F15" t="n">
-        <v>-76.1597</v>
+        <v>-72.39540000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-32.1934</v>
+        <v>-32.2087</v>
       </c>
       <c r="H15" t="n">
-        <v>-38.3441</v>
+        <v>-38.1534</v>
       </c>
       <c r="I15" t="n">
-        <v>6.150899999999995</v>
+        <v>5.944799999999998</v>
       </c>
       <c r="J15" t="n">
-        <v>52.42720000000001</v>
+        <v>49.22460000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>16.7408</v>
+        <v>14.8409</v>
       </c>
       <c r="L15" t="n">
-        <v>35.6861</v>
+        <v>34.38369999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-84.6207</v>
+        <v>-81.43320000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-55.0847</v>
+        <v>-52.99460000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-29.5352</v>
+        <v>-28.4391</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.641300000000001</v>
+        <v>-4.675600000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-71.94280000000001</v>
+        <v>-72.4679</v>
       </c>
       <c r="R15" t="n">
-        <v>67.30070000000001</v>
+        <v>67.79260000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>-22.7396</v>
+        <v>-22.8436</v>
       </c>
       <c r="T15" t="n">
-        <v>-18.0855</v>
+        <v>-17.7885</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.6538</v>
+        <v>-5.0556</v>
       </c>
       <c r="V15" t="n">
-        <v>-13.7379</v>
+        <v>-13.5978</v>
       </c>
       <c r="W15" t="n">
-        <v>40.4485</v>
+        <v>40.1011</v>
       </c>
       <c r="X15" t="n">
-        <v>-54.1865</v>
+        <v>-53.69909999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
@@ -565,67 +565,67 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8948</v>
+        <v>1.8833</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8661</v>
+        <v>5.804099999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.9711</v>
+        <v>-3.9209</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8915</v>
+        <v>3.8796</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.820399999999999</v>
+        <v>-3.8211</v>
       </c>
       <c r="I2" t="n">
-        <v>7.7119</v>
+        <v>7.7008</v>
       </c>
       <c r="J2" t="n">
-        <v>12.3988</v>
+        <v>12.3986</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5742</v>
+        <v>3.5738</v>
       </c>
       <c r="L2" t="n">
-        <v>8.8245</v>
+        <v>8.8248</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.507400000000001</v>
+        <v>-8.519</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.3948</v>
+        <v>-7.3949</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1124</v>
+        <v>-1.1241</v>
       </c>
       <c r="P2" t="n">
-        <v>5.3766</v>
+        <v>5.3807</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.4415</v>
+        <v>-4.4449</v>
       </c>
       <c r="R2" t="n">
-        <v>9.818300000000001</v>
+        <v>9.8256</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.8719</v>
+        <v>-2.8795</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.0914</v>
+        <v>-2.1497</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7806</v>
+        <v>-0.7299</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.5014</v>
+        <v>-4.4976</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.5014</v>
+        <v>-4.4976</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4614</v>
+        <v>-0.4598</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6091</v>
+        <v>-0.6085</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1477</v>
+        <v>0.1487</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.635</v>
+        <v>-1.6321</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1403</v>
+        <v>-1.1384</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4947</v>
+        <v>-0.4937</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.6323</v>
+        <v>-1.6291</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8078</v>
+        <v>-0.8063</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8245</v>
+        <v>-0.8229</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.002700000000000008</v>
+        <v>-0.002900000000000014</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3325</v>
+        <v>-0.3321</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3298</v>
+        <v>0.3292</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2338</v>
+        <v>0.2339</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2338</v>
+        <v>0.2339</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0417</v>
+        <v>-0.0436</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0517</v>
+        <v>0.052</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9298</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0649</v>
+        <v>1.0642</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1351</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5561999999999996</v>
+        <v>-0.5613000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>6.187200000000001</v>
+        <v>6.144500000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.7436</v>
+        <v>-6.7059</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3488</v>
+        <v>2.3625</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6755</v>
+        <v>-1.6715</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0242</v>
+        <v>4.0339</v>
       </c>
       <c r="J4" t="n">
-        <v>12.0253</v>
+        <v>12.0467</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7085</v>
+        <v>4.7123</v>
       </c>
       <c r="L4" t="n">
-        <v>7.3168</v>
+        <v>7.3344</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.676600000000001</v>
+        <v>-9.6844</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.383999999999999</v>
+        <v>-6.3838</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.2927</v>
+        <v>-3.3004</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.480500000000001</v>
+        <v>-7.4863</v>
       </c>
       <c r="Q4" t="n">
-        <v>-14.961</v>
+        <v>-14.9726</v>
       </c>
       <c r="R4" t="n">
-        <v>7.4805</v>
+        <v>7.4864</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3673</v>
+        <v>-2.3774</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.6615</v>
+        <v>-1.7061</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.706</v>
+        <v>-0.6714</v>
       </c>
       <c r="V4" t="n">
-        <v>6.9428</v>
+        <v>6.9399</v>
       </c>
       <c r="W4" t="n">
-        <v>10.7844</v>
+        <v>10.7764</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.8416</v>
+        <v>-3.8366</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.4224</v>
+        <v>-2.4265</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3408000000000002</v>
+        <v>0.3204000000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.7633</v>
+        <v>-2.7469</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.08250000000000002</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0293000000000001</v>
+        <v>0.02870000000000006</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.109</v>
+        <v>-0.1112000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0969</v>
+        <v>2.0984</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5587</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5382</v>
+        <v>1.5374</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1767</v>
+        <v>-2.1809</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5296000000000001</v>
+        <v>-0.5321</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6472</v>
+        <v>-1.6488</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8702</v>
+        <v>-1.8715</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.207800000000001</v>
+        <v>-4.211</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3377</v>
+        <v>2.3395</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8907</v>
+        <v>-0.8926000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2106</v>
+        <v>-0.2274</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6800999999999999</v>
+        <v>-0.6652</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4181999999999997</v>
+        <v>0.4201999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6624</v>
+        <v>2.6605</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2442</v>
+        <v>-2.2403</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.7182</v>
+        <v>-3.7177</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4536</v>
+        <v>-2.477</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2648</v>
+        <v>-1.2411</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.8448</v>
+        <v>-3.8456</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7211</v>
+        <v>-1.7217</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1238</v>
+        <v>-2.1237</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1426000000000001</v>
+        <v>-0.1369000000000002</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6358</v>
+        <v>1.6346</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.7784</v>
+        <v>-1.7716</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.7022</v>
+        <v>-3.7086</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.357</v>
+        <v>-3.3566</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3454</v>
+        <v>-0.3520000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1039</v>
+        <v>2.1054</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6364</v>
+        <v>-1.6375</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7403</v>
+        <v>3.743</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2445999999999999</v>
+        <v>-0.2474000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7394</v>
+        <v>-1.7666</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4946</v>
+        <v>1.5192</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7325</v>
+        <v>-1.7307</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0649</v>
+        <v>1.0642</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7974</v>
+        <v>-2.7949</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.4198</v>
+        <v>-5.4228</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.721</v>
+        <v>-0.7395999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.6989</v>
+        <v>-4.6833</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6086</v>
+        <v>-2.6087</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2975</v>
+        <v>-2.2969</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3110999999999999</v>
+        <v>-0.3115</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0305</v>
+        <v>1.0327</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3797</v>
+        <v>1.3781</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3493000000000001</v>
+        <v>-0.3455</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.639</v>
+        <v>-3.6414</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.6772</v>
+        <v>-3.6754</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03820000000000004</v>
+        <v>0.03399999999999997</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4675</v>
+        <v>0.4679</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.4026</v>
+        <v>-1.4036</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8701</v>
+        <v>1.8715</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0839</v>
+        <v>-0.08959999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3489</v>
+        <v>-0.3685999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2649</v>
+        <v>0.279</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.1948</v>
+        <v>-3.1926</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.1948</v>
+        <v>-3.1926</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.5467</v>
+        <v>-6.547499999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.17</v>
+        <v>-6.1835</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3767</v>
+        <v>-0.3639999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5082</v>
+        <v>-1.5049</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9836</v>
+        <v>-1.9819</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4755</v>
+        <v>0.4772</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7342000000000001</v>
+        <v>-0.7269</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03679999999999972</v>
+        <v>0.03880000000000017</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7708000000000002</v>
+        <v>-0.7657</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.774</v>
+        <v>-0.7778999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0203</v>
+        <v>-2.0208</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2463</v>
+        <v>1.2428</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.8052</v>
+        <v>-2.8074</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.6754</v>
+        <v>-4.679</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8702</v>
+        <v>1.8715</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4307</v>
+        <v>-1.4343</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7606000000000002</v>
+        <v>-0.7776</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6701</v>
+        <v>-0.6567000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8026</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8026</v>
+        <v>-0.8008999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.725899999999999</v>
+        <v>-6.721399999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>5.557700000000001</v>
+        <v>5.5091</v>
       </c>
       <c r="F9" t="n">
-        <v>-12.2835</v>
+        <v>-12.2304</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1985</v>
+        <v>-1.1981</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.02450000000000008</v>
+        <v>-0.03039999999999987</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1741</v>
+        <v>-1.1678</v>
       </c>
       <c r="J9" t="n">
-        <v>10.3306</v>
+        <v>10.3408</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5392</v>
+        <v>5.5351</v>
       </c>
       <c r="L9" t="n">
-        <v>4.791499999999999</v>
+        <v>4.8058</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.5291</v>
+        <v>-11.539</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.5636</v>
+        <v>-5.5655</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.9656</v>
+        <v>-5.973599999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2077</v>
+        <v>4.2111</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9741</v>
+        <v>-3.977</v>
       </c>
       <c r="R9" t="n">
-        <v>8.181800000000001</v>
+        <v>8.1881</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.9612</v>
+        <v>-2.9683</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.9288</v>
+        <v>-2.9829</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0323</v>
+        <v>0.01459999999999997</v>
       </c>
       <c r="V9" t="n">
-        <v>-6.7741</v>
+        <v>-6.7659</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1299</v>
+        <v>2.1284</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.904</v>
+        <v>-8.894299999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.222499999999999</v>
+        <v>-7.2209</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7051999999999996</v>
+        <v>0.6701999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.9277</v>
+        <v>-7.8909</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2042</v>
+        <v>-4.191599999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9748</v>
+        <v>-2.9697</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2293</v>
+        <v>-1.2218</v>
       </c>
       <c r="J10" t="n">
-        <v>5.7913</v>
+        <v>5.810700000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2374</v>
+        <v>1.2437</v>
       </c>
       <c r="L10" t="n">
-        <v>4.553900000000001</v>
+        <v>4.5671</v>
       </c>
       <c r="M10" t="n">
-        <v>-9.9955</v>
+        <v>-10.0024</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.2122</v>
+        <v>-4.2133</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.7834</v>
+        <v>-5.789</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1039</v>
+        <v>-2.1056</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.9482</v>
+        <v>-7.9541</v>
       </c>
       <c r="R10" t="n">
-        <v>5.8442</v>
+        <v>5.8486</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9302</v>
+        <v>-1.9374</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.0732</v>
+        <v>-2.1151</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1429999999999999</v>
+        <v>0.1777</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0154</v>
+        <v>1.0138</v>
       </c>
       <c r="W10" t="n">
-        <v>4.9349</v>
+        <v>4.9288</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.9195</v>
+        <v>-3.915</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.2503</v>
+        <v>-7.245900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9600000000000004</v>
+        <v>-0.9989</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.2904</v>
+        <v>-6.2469</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.8627</v>
+        <v>-6.8569</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.0655</v>
+        <v>-7.0562</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2028000000000001</v>
+        <v>0.1991000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3</v>
+        <v>-1.2818</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.3304</v>
+        <v>-3.3172</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0303</v>
+        <v>2.0352</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.5625</v>
+        <v>-5.5751</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.7349</v>
+        <v>-3.7388</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8277</v>
+        <v>-1.8364</v>
       </c>
       <c r="P11" t="n">
-        <v>4.9091</v>
+        <v>4.9127</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5714</v>
+        <v>-2.5734</v>
       </c>
       <c r="R11" t="n">
-        <v>7.4805</v>
+        <v>7.4862</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7823</v>
+        <v>-1.7901</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0858</v>
+        <v>-1.1372</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6966000000000001</v>
+        <v>-0.6527999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.5143</v>
+        <v>-3.5118</v>
       </c>
       <c r="W11" t="n">
-        <v>3.9975</v>
+        <v>3.9935</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.5116</v>
+        <v>-7.5053</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.131599999999999</v>
+        <v>-9.130500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.830400000000001</v>
+        <v>-4.8661</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.300999999999999</v>
+        <v>-4.2645</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.346</v>
+        <v>-2.326</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.442600000000001</v>
+        <v>-8.422699999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>6.0966</v>
+        <v>6.0967</v>
       </c>
       <c r="J12" t="n">
-        <v>6.4089</v>
+        <v>6.438800000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.383</v>
+        <v>-3.3614</v>
       </c>
       <c r="L12" t="n">
-        <v>9.792</v>
+        <v>9.8002</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.7547</v>
+        <v>-8.764900000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.0595</v>
+        <v>-5.061500000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.6952</v>
+        <v>-3.7035</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.6754</v>
+        <v>-4.679</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.0909</v>
+        <v>-13.1011</v>
       </c>
       <c r="R12" t="n">
-        <v>8.415700000000001</v>
+        <v>8.4221</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.1623</v>
+        <v>-4.1754</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.5432</v>
+        <v>-2.595</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.619</v>
+        <v>-1.5805</v>
       </c>
       <c r="V12" t="n">
-        <v>2.0519</v>
+        <v>2.05</v>
       </c>
       <c r="W12" t="n">
-        <v>4.3947</v>
+        <v>4.3912</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3429</v>
+        <v>-2.3412</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.4191</v>
+        <v>-10.4116</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2604</v>
+        <v>-1.2951</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.1587</v>
+        <v>-9.116400000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.0014</v>
+        <v>-6.9905</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.6624</v>
+        <v>-2.6512</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.338900000000001</v>
+        <v>-4.339399999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6995</v>
+        <v>1.7182</v>
       </c>
       <c r="K13" t="n">
-        <v>3.369</v>
+        <v>3.3783</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6696</v>
+        <v>-1.6603</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.700900000000001</v>
+        <v>-8.708600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.0315</v>
+        <v>-6.0296</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.6695</v>
+        <v>-2.6791</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1689</v>
+        <v>1.1697</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.6105</v>
+        <v>-5.614599999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>6.7792</v>
+        <v>6.7844</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7607</v>
+        <v>-0.7652000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8223999999999999</v>
+        <v>-0.8654000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06160000000000004</v>
+        <v>0.1002</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.8259</v>
+        <v>-3.8256</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4728</v>
+        <v>3.4669</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.2988</v>
+        <v>-7.2925</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.3458</v>
+        <v>-15.3485</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.5824</v>
+        <v>-2.6151</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.7634</v>
+        <v>-12.7335</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.159899999999999</v>
+        <v>-7.1487</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.374499999999999</v>
+        <v>-4.3701</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.7853</v>
+        <v>-2.7788</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2519</v>
+        <v>1.2683</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3228</v>
+        <v>0.3266</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9290999999999999</v>
+        <v>0.9417000000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.411899999999999</v>
+        <v>-8.4171</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.6975</v>
+        <v>-4.6967</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7143</v>
+        <v>-3.7204</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.2079</v>
+        <v>-4.2111</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.9481</v>
+        <v>-7.9541</v>
       </c>
       <c r="R14" t="n">
-        <v>3.7403</v>
+        <v>3.7431</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.3677</v>
+        <v>-3.3782</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.481</v>
+        <v>-1.5188</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.8867</v>
+        <v>-1.8593</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.6105000000000003</v>
       </c>
       <c r="W14" t="n">
-        <v>5.5947</v>
+        <v>5.5898</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.2052</v>
+        <v>-6.2003</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-73.32509999999999</v>
+        <v>-73.33109999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9299000000000017</v>
+        <v>-1.335500000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-72.39540000000001</v>
+        <v>-71.99600000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-32.2087</v>
+        <v>-32.1435</v>
       </c>
       <c r="H15" t="n">
-        <v>-38.1534</v>
+        <v>-38.1031</v>
       </c>
       <c r="I15" t="n">
-        <v>5.944799999999998</v>
+        <v>5.959799999999998</v>
       </c>
       <c r="J15" t="n">
-        <v>49.22460000000001</v>
+        <v>49.3785</v>
       </c>
       <c r="K15" t="n">
-        <v>14.8409</v>
+        <v>14.8974</v>
       </c>
       <c r="L15" t="n">
-        <v>34.38369999999999</v>
+        <v>34.4806</v>
       </c>
       <c r="M15" t="n">
-        <v>-81.43320000000001</v>
+        <v>-81.52220000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-52.99460000000001</v>
+        <v>-53.0011</v>
       </c>
       <c r="O15" t="n">
-        <v>-28.4391</v>
+        <v>-28.5213</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.675600000000001</v>
+        <v>-4.679499999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-72.4679</v>
+        <v>-72.52289999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>67.79260000000001</v>
+        <v>67.8439</v>
       </c>
       <c r="S15" t="n">
-        <v>-22.8436</v>
+        <v>-22.9269</v>
       </c>
       <c r="T15" t="n">
-        <v>-17.7885</v>
+        <v>-18.254</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.0556</v>
+        <v>-4.6731</v>
       </c>
       <c r="V15" t="n">
-        <v>-13.5978</v>
+        <v>-13.5819</v>
       </c>
       <c r="W15" t="n">
-        <v>40.1011</v>
+        <v>40.0639</v>
       </c>
       <c r="X15" t="n">
-        <v>-53.69909999999999</v>
+        <v>-53.6459</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total_NP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Off_NP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Def_NP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Net_Shooting</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Net_2P</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net_3P</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Off_Shooting</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Off_2P</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Off_3P</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Def_Shooting</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Def_2P</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Def_3P</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Net_TOV</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Off_TOV</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Def_TOV</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Net_ORB</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Off_ORB</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Def_ORB</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Net_FT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Off_FT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Def_FT</t>
         </is>
@@ -565,67 +553,67 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8833</v>
+        <v>1.8778</v>
       </c>
       <c r="E2" t="n">
-        <v>5.804099999999999</v>
+        <v>5.7946</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.9209</v>
+        <v>-3.9165</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8796</v>
+        <v>3.8749</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.8211</v>
+        <v>-3.823</v>
       </c>
       <c r="I2" t="n">
-        <v>7.7008</v>
+        <v>7.698099999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>12.3986</v>
+        <v>12.4012</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5738</v>
+        <v>3.5751</v>
       </c>
       <c r="L2" t="n">
-        <v>8.8248</v>
+        <v>8.8261</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.519</v>
+        <v>-8.526299999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.3949</v>
+        <v>-7.3983</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1241</v>
+        <v>-1.1279</v>
       </c>
       <c r="P2" t="n">
-        <v>5.3807</v>
+        <v>5.3811</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.4449</v>
+        <v>-4.4453</v>
       </c>
       <c r="R2" t="n">
-        <v>9.8256</v>
+        <v>9.8264</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.8795</v>
+        <v>-2.8808</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.1497</v>
+        <v>-2.1615</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7299</v>
+        <v>-0.7195</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.4976</v>
+        <v>-4.4973</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.4976</v>
+        <v>-4.4973</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +631,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4598</v>
+        <v>-0.4594</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6085</v>
+        <v>-0.6081</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1487</v>
+        <v>0.1486</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.6321</v>
+        <v>-1.6314</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1384</v>
+        <v>-1.1379</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4937</v>
+        <v>-0.4935</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.6291</v>
+        <v>-1.6283</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8063</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8229</v>
+        <v>-0.8225</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.002900000000000014</v>
+        <v>-0.003099999999999992</v>
       </c>
       <c r="N3" t="n">
         <v>-0.3321</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3292</v>
+        <v>0.329</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2339</v>
+        <v>0.234</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2339</v>
+        <v>0.234</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0436</v>
+        <v>-0.0439</v>
       </c>
       <c r="U3" t="n">
-        <v>0.052</v>
+        <v>0.0521</v>
       </c>
       <c r="V3" t="n">
         <v>0.9298</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0642</v>
+        <v>1.0641</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1344</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +709,67 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5613000000000001</v>
+        <v>-0.5591000000000008</v>
       </c>
       <c r="E4" t="n">
         <v>6.144500000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.7059</v>
+        <v>-6.7036</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3625</v>
+        <v>2.3672</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6715</v>
+        <v>-1.6704</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0339</v>
+        <v>4.0377</v>
       </c>
       <c r="J4" t="n">
-        <v>12.0467</v>
+        <v>12.0574</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7123</v>
+        <v>4.7164</v>
       </c>
       <c r="L4" t="n">
-        <v>7.3344</v>
+        <v>7.341099999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.6844</v>
+        <v>-9.690099999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.3838</v>
+        <v>-6.386699999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.3004</v>
+        <v>-3.3033</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.4863</v>
+        <v>-7.4869</v>
       </c>
       <c r="Q4" t="n">
-        <v>-14.9726</v>
+        <v>-14.9736</v>
       </c>
       <c r="R4" t="n">
-        <v>7.4864</v>
+        <v>7.486899999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3774</v>
+        <v>-2.3791</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7061</v>
+        <v>-1.7151</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6714</v>
+        <v>-0.6642</v>
       </c>
       <c r="V4" t="n">
-        <v>6.9399</v>
+        <v>6.9396</v>
       </c>
       <c r="W4" t="n">
-        <v>10.7764</v>
+        <v>10.7758</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.8366</v>
+        <v>-3.8363</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +787,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.4265</v>
+        <v>-2.4278</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3204000000000002</v>
+        <v>0.3176999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.7469</v>
+        <v>-2.7455</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.08250000000000002</v>
+        <v>-0.08350000000000002</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02870000000000006</v>
+        <v>0.02859999999999996</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1112000000000001</v>
+        <v>-0.1121</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0984</v>
+        <v>2.0996</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5621999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5374</v>
+        <v>1.5373</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1809</v>
+        <v>-2.1831</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5321</v>
+        <v>-0.5336</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6488</v>
+        <v>-1.6494</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8715</v>
+        <v>-1.8717</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.211</v>
+        <v>-4.2113</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3395</v>
+        <v>2.3397</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8926000000000001</v>
+        <v>-0.893</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2274</v>
+        <v>-0.2308</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6652</v>
+        <v>-0.6621</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4201999999999999</v>
+        <v>0.4203000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6605</v>
+        <v>2.6604</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2403</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +865,67 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.7177</v>
+        <v>-3.7194</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.477</v>
+        <v>-2.4804</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2411</v>
+        <v>-1.2391</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.8456</v>
+        <v>-3.8468</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7217</v>
+        <v>-1.7229</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1237</v>
+        <v>-2.124</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1369000000000002</v>
+        <v>-0.1346000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6346</v>
+        <v>1.6349</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.7716</v>
+        <v>-1.7697</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.7086</v>
+        <v>-3.7121</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.3566</v>
+        <v>-3.3578</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3520000000000001</v>
+        <v>-0.3543000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1054</v>
+        <v>2.1057</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6375</v>
+        <v>-1.6378</v>
       </c>
       <c r="R6" t="n">
-        <v>3.743</v>
+        <v>3.7435</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2474000000000001</v>
+        <v>-0.2478</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7666</v>
+        <v>-1.772</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5192</v>
+        <v>1.5242</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7307</v>
+        <v>-1.7305</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0642</v>
+        <v>1.0641</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7949</v>
+        <v>-2.7946</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +943,67 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.4228</v>
+        <v>-5.4248</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7395999999999999</v>
+        <v>-0.7426000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.6833</v>
+        <v>-4.6821</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6087</v>
+        <v>-2.6097</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2969</v>
+        <v>-2.2978</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3115</v>
+        <v>-0.3118</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0327</v>
+        <v>1.0338</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3781</v>
+        <v>1.378</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3455</v>
+        <v>-0.3444</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.6414</v>
+        <v>-3.6434</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.6754</v>
+        <v>-3.676</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03399999999999997</v>
+        <v>0.03260000000000005</v>
       </c>
       <c r="P7" t="n">
         <v>0.4679</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.4036</v>
+        <v>-1.4038</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8715</v>
+        <v>1.8717</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.08959999999999999</v>
+        <v>-0.09069999999999998</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3685999999999999</v>
+        <v>-0.3727000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.279</v>
+        <v>0.282</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.1926</v>
+        <v>-3.1924</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.1926</v>
+        <v>-3.1924</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1021,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.547499999999999</v>
+        <v>-6.5476</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.1835</v>
+        <v>-6.184699999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3639999999999999</v>
+        <v>-0.363</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5049</v>
+        <v>-1.5044</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9819</v>
+        <v>-1.982</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4772</v>
+        <v>0.4776</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7269</v>
+        <v>-0.7243999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03880000000000017</v>
+        <v>0.03989999999999982</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7657</v>
+        <v>-0.7641</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7778999999999999</v>
+        <v>-0.78</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0208</v>
+        <v>-2.0218</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2428</v>
+        <v>1.2419</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.8074</v>
+        <v>-2.8075</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.679</v>
+        <v>-4.6792</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8715</v>
+        <v>1.8718</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4343</v>
+        <v>-1.4349</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7776</v>
+        <v>-0.781</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6567000000000001</v>
+        <v>-0.6538999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.8007</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.8007</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1099,67 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.721399999999999</v>
+        <v>-6.7225</v>
       </c>
       <c r="E9" t="n">
-        <v>5.5091</v>
+        <v>5.5037</v>
       </c>
       <c r="F9" t="n">
-        <v>-12.2304</v>
+        <v>-12.2261</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1981</v>
+        <v>-1.1991</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.03039999999999987</v>
+        <v>-0.03320000000000012</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1678</v>
+        <v>-1.165900000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>10.3408</v>
+        <v>10.3465</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5351</v>
+        <v>5.5357</v>
       </c>
       <c r="L9" t="n">
-        <v>4.8058</v>
+        <v>4.811</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.539</v>
+        <v>-11.5456</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.5655</v>
+        <v>-5.5688</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.973599999999999</v>
+        <v>-5.9767</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2111</v>
+        <v>4.2113</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.977</v>
+        <v>-3.9774</v>
       </c>
       <c r="R9" t="n">
-        <v>8.1881</v>
+        <v>8.188800000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.9683</v>
+        <v>-2.9694</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.9829</v>
+        <v>-2.9939</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01459999999999997</v>
+        <v>0.02449999999999997</v>
       </c>
       <c r="V9" t="n">
-        <v>-6.7659</v>
+        <v>-6.7652</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1284</v>
+        <v>2.1283</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.894299999999999</v>
+        <v>-8.8935</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1177,67 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.2209</v>
+        <v>-7.2189</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6701999999999999</v>
+        <v>0.6692999999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.8909</v>
+        <v>-7.8882</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.191599999999999</v>
+        <v>-4.188300000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9697</v>
+        <v>-2.9686</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2218</v>
+        <v>-1.2197</v>
       </c>
       <c r="J10" t="n">
-        <v>5.810700000000001</v>
+        <v>5.819000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2437</v>
+        <v>1.2473</v>
       </c>
       <c r="L10" t="n">
-        <v>4.5671</v>
+        <v>4.5717</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.0024</v>
+        <v>-10.0073</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.2133</v>
+        <v>-4.2159</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.789</v>
+        <v>-5.7914</v>
       </c>
       <c r="P10" t="n">
         <v>-2.1056</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.9541</v>
+        <v>-7.9547</v>
       </c>
       <c r="R10" t="n">
-        <v>5.8486</v>
+        <v>5.8492</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9374</v>
+        <v>-1.9387</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.1151</v>
+        <v>-2.1235</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1777</v>
+        <v>0.1849</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0138</v>
+        <v>1.0136</v>
       </c>
       <c r="W10" t="n">
-        <v>4.9288</v>
+        <v>4.9282</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.915</v>
+        <v>-3.9147</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1255,67 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.245900000000001</v>
+        <v>-7.246600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9989</v>
+        <v>-1.0031</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.2469</v>
+        <v>-6.2433</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.8569</v>
+        <v>-6.8566</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.0562</v>
+        <v>-7.054499999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1991000000000001</v>
+        <v>0.1978999999999997</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2818</v>
+        <v>-1.275</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.3172</v>
+        <v>-3.3122</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0352</v>
+        <v>2.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.5751</v>
+        <v>-5.5817</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.7388</v>
+        <v>-3.7425</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8364</v>
+        <v>-1.8392</v>
       </c>
       <c r="P11" t="n">
-        <v>4.9127</v>
+        <v>4.9132</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5734</v>
+        <v>-2.5736</v>
       </c>
       <c r="R11" t="n">
-        <v>7.4862</v>
+        <v>7.4869</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7901</v>
+        <v>-1.7915</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1372</v>
+        <v>-1.1477</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6527999999999999</v>
+        <v>-0.6438</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.5118</v>
+        <v>-3.5117</v>
       </c>
       <c r="W11" t="n">
-        <v>3.9935</v>
+        <v>3.9932</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.5053</v>
+        <v>-7.5049</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1333,67 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.130500000000001</v>
+        <v>-9.1266</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8661</v>
+        <v>-4.864699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2645</v>
+        <v>-4.261900000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.326</v>
+        <v>-2.3193</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.422699999999999</v>
+        <v>-8.4169</v>
       </c>
       <c r="I12" t="n">
-        <v>6.0967</v>
+        <v>6.0974</v>
       </c>
       <c r="J12" t="n">
-        <v>6.438800000000001</v>
+        <v>6.451700000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.3614</v>
+        <v>-3.3522</v>
       </c>
       <c r="L12" t="n">
-        <v>9.8002</v>
+        <v>9.803899999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.764900000000001</v>
+        <v>-8.771000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.061500000000001</v>
+        <v>-5.0646</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.7035</v>
+        <v>-3.7065</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.679</v>
+        <v>-4.6793</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.1011</v>
+        <v>-13.102</v>
       </c>
       <c r="R12" t="n">
-        <v>8.4221</v>
+        <v>8.422699999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.1754</v>
+        <v>-4.1779</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.595</v>
+        <v>-2.6055</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5805</v>
+        <v>-1.5724</v>
       </c>
       <c r="V12" t="n">
-        <v>2.05</v>
+        <v>2.0497</v>
       </c>
       <c r="W12" t="n">
-        <v>4.3912</v>
+        <v>4.390700000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3412</v>
+        <v>-2.3411</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1411,67 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.4116</v>
+        <v>-10.4087</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2951</v>
+        <v>-1.2958</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.116400000000001</v>
+        <v>-9.1128</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.9905</v>
+        <v>-6.986999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.6512</v>
+        <v>-2.6468</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.339399999999999</v>
+        <v>-4.3401</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7182</v>
+        <v>1.7271</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3783</v>
+        <v>3.3847</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6603</v>
+        <v>-1.6576</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.708600000000001</v>
+        <v>-8.713899999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.0296</v>
+        <v>-6.0314</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.6791</v>
+        <v>-2.6825</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1697</v>
+        <v>1.1698</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.614599999999999</v>
+        <v>-5.6152</v>
       </c>
       <c r="R13" t="n">
-        <v>6.7844</v>
+        <v>6.785</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7652000000000001</v>
+        <v>-0.7659</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8654000000000001</v>
+        <v>-0.8741</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1002</v>
+        <v>0.1082000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-3.8256</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4669</v>
+        <v>3.4665</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.2925</v>
+        <v>-7.2921</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1489,67 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.3485</v>
+        <v>-15.3486</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.6151</v>
+        <v>-2.6175</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.7335</v>
+        <v>-12.7312</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.1487</v>
+        <v>-7.1468</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.3701</v>
+        <v>-4.369899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.7788</v>
+        <v>-2.7768</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2683</v>
+        <v>1.2745</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3266</v>
+        <v>0.3286000000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9417000000000002</v>
+        <v>0.9458</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.4171</v>
+        <v>-8.421200000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.6967</v>
+        <v>-4.6985</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7204</v>
+        <v>-3.7227</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.2111</v>
+        <v>-4.211399999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.9541</v>
+        <v>-7.9548</v>
       </c>
       <c r="R14" t="n">
-        <v>3.7431</v>
+        <v>3.7435</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.3782</v>
+        <v>-3.3799</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5188</v>
+        <v>-1.5266</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.8593</v>
+        <v>-1.8534</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6105000000000003</v>
+        <v>-0.6106</v>
       </c>
       <c r="W14" t="n">
-        <v>5.5898</v>
+        <v>5.5893</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.2003</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1567,67 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-73.33109999999999</v>
+        <v>-73.3322</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.335500000000001</v>
+        <v>-1.367099999999997</v>
       </c>
       <c r="F15" t="n">
-        <v>-71.99600000000001</v>
+        <v>-71.96469999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-32.1435</v>
+        <v>-32.1308</v>
       </c>
       <c r="H15" t="n">
-        <v>-38.1031</v>
+        <v>-38.0953</v>
       </c>
       <c r="I15" t="n">
-        <v>5.959799999999998</v>
+        <v>5.9648</v>
       </c>
       <c r="J15" t="n">
-        <v>49.3785</v>
+        <v>49.44850000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>14.8974</v>
+        <v>14.9325</v>
       </c>
       <c r="L15" t="n">
-        <v>34.4806</v>
+        <v>34.51579999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-81.52220000000001</v>
+        <v>-81.57879999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-53.0011</v>
+        <v>-53.028</v>
       </c>
       <c r="O15" t="n">
-        <v>-28.5213</v>
+        <v>-28.5504</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.679499999999999</v>
+        <v>-4.679399999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-72.52289999999999</v>
+        <v>-72.52870000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>67.8439</v>
+        <v>67.8501</v>
       </c>
       <c r="S15" t="n">
-        <v>-22.9269</v>
+        <v>-22.9414</v>
       </c>
       <c r="T15" t="n">
-        <v>-18.254</v>
+        <v>-18.3483</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.6731</v>
+        <v>-4.593400000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-13.5819</v>
+        <v>-13.581</v>
       </c>
       <c r="W15" t="n">
-        <v>40.0639</v>
+        <v>40.0606</v>
       </c>
       <c r="X15" t="n">
-        <v>-53.6459</v>
+        <v>-53.6419</v>
       </c>
     </row>
   </sheetData>
